--- a/testdata/개정과목체계.xlsx
+++ b/testdata/개정과목체계.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\jinuchoi\projects\PB_AI\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69983FDE-E9FA-47EB-B272-2F4B2492B7DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD2147CF-89B9-4AE6-AA61-BA3ACABA1F1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14303" yWindow="-1402" windowWidth="21795" windowHeight="12974" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3895,9 +3895,6 @@
     <t>Current portion of exchangeable bond</t>
   </si>
   <si>
-    <t>dart_CurentPortionOfFinanceLeaseLiabilities</t>
-  </si>
-  <si>
     <t>CurentPortionOfFinanceLeaseLiabilities</t>
   </si>
   <si>
@@ -3907,9 +3904,6 @@
     <t>Curent portion of finance lease liabilities</t>
   </si>
   <si>
-    <t>ifrs_CurrentLeaseLiabilities</t>
-  </si>
-  <si>
     <t>CurrentLeaseLiabilities</t>
   </si>
   <si>
@@ -4282,9 +4276,6 @@
     <t>일반기업회계기준 33.14</t>
   </si>
   <si>
-    <t>ifrs_NoncurrentLiabilities</t>
-  </si>
-  <si>
     <t>NoncurrentLiabilities</t>
   </si>
   <si>
@@ -4573,9 +4564,6 @@
     <t>Present value discounts, long-term rent received in advance</t>
   </si>
   <si>
-    <t>dart_LongTermBorrowingsGross</t>
-  </si>
-  <si>
     <t>LongTermBorrowingsGross</t>
   </si>
   <si>
@@ -4594,9 +4582,6 @@
     <t>Present value discounts, long-term borrowings</t>
   </si>
   <si>
-    <t>dart_BondsIssued</t>
-  </si>
-  <si>
     <t>BondsIssued</t>
   </si>
   <si>
@@ -5236,9 +5221,6 @@
     <t>Non-current emission liabilities</t>
   </si>
   <si>
-    <t>ifrs_Liabilities</t>
-  </si>
-  <si>
     <t>Liabilities</t>
   </si>
   <si>
@@ -5858,9 +5840,6 @@
   </si>
   <si>
     <t>K-IFRS 1001 문단 54 (17)</t>
-  </si>
-  <si>
-    <t>ifrs_Equity</t>
   </si>
   <si>
     <t>Equity</t>
@@ -5925,6 +5904,34 @@
   </si>
   <si>
     <t>ifrs_ShorttermBorrowings</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ifrs_NoncurrentLiabilities</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>dart_BondsIssued</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>dart_LongTermBorrowingsGross</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>dart_CurentPortionOfFinanceLeaseLiabilities</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ifrs_Liabilities</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ifrs_Equity</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ifrs_CurrentLeaseLiabilities</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -6298,14 +6305,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I520"/>
-  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="50.5" customWidth="1"/>
     <col min="5" max="5" width="2" customWidth="1"/>
     <col min="6" max="6" width="27.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6331,7 +6338,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -6357,7 +6364,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -6383,7 +6390,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -6394,7 +6401,7 @@
         <v>9</v>
       </c>
       <c r="D4" t="s">
-        <v>1954</v>
+        <v>1947</v>
       </c>
       <c r="E4" t="s">
         <v>19</v>
@@ -6412,7 +6419,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -6423,7 +6430,7 @@
         <v>9</v>
       </c>
       <c r="D5" t="s">
-        <v>1955</v>
+        <v>1948</v>
       </c>
       <c r="E5" t="s">
         <v>24</v>
@@ -6441,7 +6448,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -6470,7 +6477,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -6499,7 +6506,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -6528,7 +6535,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -6557,7 +6564,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -6586,7 +6593,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -6597,7 +6604,7 @@
         <v>9</v>
       </c>
       <c r="D11" t="s">
-        <v>1956</v>
+        <v>1949</v>
       </c>
       <c r="E11" t="s">
         <v>51</v>
@@ -6615,7 +6622,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>10</v>
       </c>
@@ -6644,7 +6651,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>11</v>
       </c>
@@ -6673,7 +6680,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>12</v>
       </c>
@@ -6702,7 +6709,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>13</v>
       </c>
@@ -6731,7 +6738,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>14</v>
       </c>
@@ -6760,7 +6767,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>15</v>
       </c>
@@ -6789,7 +6796,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>16</v>
       </c>
@@ -6818,7 +6825,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>17</v>
       </c>
@@ -6847,7 +6854,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>18</v>
       </c>
@@ -6876,7 +6883,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>19</v>
       </c>
@@ -6905,7 +6912,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>20</v>
       </c>
@@ -6934,7 +6941,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>21</v>
       </c>
@@ -6963,7 +6970,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>22</v>
       </c>
@@ -6992,7 +6999,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>23</v>
       </c>
@@ -7021,7 +7028,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>24</v>
       </c>
@@ -7050,7 +7057,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>25</v>
       </c>
@@ -7079,7 +7086,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>26</v>
       </c>
@@ -7108,7 +7115,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>27</v>
       </c>
@@ -7137,7 +7144,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>28</v>
       </c>
@@ -7166,7 +7173,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>29</v>
       </c>
@@ -7195,7 +7202,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>30</v>
       </c>
@@ -7224,7 +7231,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>31</v>
       </c>
@@ -7253,7 +7260,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>32</v>
       </c>
@@ -7282,7 +7289,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>33</v>
       </c>
@@ -7311,7 +7318,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>34</v>
       </c>
@@ -7340,7 +7347,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>35</v>
       </c>
@@ -7369,7 +7376,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>36</v>
       </c>
@@ -7398,7 +7405,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>37</v>
       </c>
@@ -7427,7 +7434,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>38</v>
       </c>
@@ -7456,7 +7463,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>39</v>
       </c>
@@ -7485,7 +7492,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <v>40</v>
       </c>
@@ -7514,7 +7521,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>41</v>
       </c>
@@ -7543,7 +7550,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <v>42</v>
       </c>
@@ -7572,7 +7579,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
         <v>43</v>
       </c>
@@ -7601,7 +7608,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
         <v>44</v>
       </c>
@@ -7612,7 +7619,7 @@
         <v>9</v>
       </c>
       <c r="D46" t="s">
-        <v>1957</v>
+        <v>1950</v>
       </c>
       <c r="E46" t="s">
         <v>178</v>
@@ -7630,7 +7637,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
         <v>45</v>
       </c>
@@ -7659,7 +7666,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
         <v>46</v>
       </c>
@@ -7688,7 +7695,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
         <v>47</v>
       </c>
@@ -7717,7 +7724,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
         <v>48</v>
       </c>
@@ -7746,7 +7753,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
         <v>49</v>
       </c>
@@ -7775,7 +7782,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
         <v>50</v>
       </c>
@@ -7804,7 +7811,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
         <v>51</v>
       </c>
@@ -7833,7 +7840,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
         <v>52</v>
       </c>
@@ -7862,7 +7869,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
         <v>53</v>
       </c>
@@ -7891,7 +7898,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
         <v>54</v>
       </c>
@@ -7920,7 +7927,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57" s="1">
         <v>55</v>
       </c>
@@ -7949,7 +7956,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
         <v>56</v>
       </c>
@@ -7978,7 +7985,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59" s="1">
         <v>57</v>
       </c>
@@ -8007,7 +8014,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60" s="1">
         <v>58</v>
       </c>
@@ -8036,7 +8043,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61" s="1">
         <v>59</v>
       </c>
@@ -8065,7 +8072,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62" s="1">
         <v>60</v>
       </c>
@@ -8094,7 +8101,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63" s="1">
         <v>61</v>
       </c>
@@ -8123,7 +8130,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64" s="1">
         <v>62</v>
       </c>
@@ -8152,7 +8159,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A65" s="1">
         <v>63</v>
       </c>
@@ -8181,7 +8188,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A66" s="1">
         <v>64</v>
       </c>
@@ -8210,7 +8217,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A67" s="1">
         <v>65</v>
       </c>
@@ -8239,7 +8246,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A68" s="1">
         <v>66</v>
       </c>
@@ -8268,7 +8275,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A69" s="1">
         <v>67</v>
       </c>
@@ -8297,7 +8304,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A70" s="1">
         <v>68</v>
       </c>
@@ -8326,7 +8333,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A71" s="1">
         <v>69</v>
       </c>
@@ -8355,7 +8362,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A72" s="1">
         <v>70</v>
       </c>
@@ -8384,7 +8391,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A73" s="1">
         <v>71</v>
       </c>
@@ -8413,7 +8420,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A74" s="1">
         <v>72</v>
       </c>
@@ -8442,7 +8449,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A75" s="1">
         <v>73</v>
       </c>
@@ -8471,7 +8478,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A76" s="1">
         <v>74</v>
       </c>
@@ -8500,7 +8507,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A77" s="1">
         <v>75</v>
       </c>
@@ -8529,7 +8536,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A78" s="1">
         <v>76</v>
       </c>
@@ -8558,7 +8565,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A79" s="1">
         <v>77</v>
       </c>
@@ -8587,7 +8594,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A80" s="1">
         <v>78</v>
       </c>
@@ -8616,7 +8623,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A81" s="1">
         <v>79</v>
       </c>
@@ -8645,7 +8652,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A82" s="1">
         <v>80</v>
       </c>
@@ -8674,7 +8681,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A83" s="1">
         <v>81</v>
       </c>
@@ -8703,7 +8710,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A84" s="1">
         <v>82</v>
       </c>
@@ -8732,7 +8739,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A85" s="1">
         <v>83</v>
       </c>
@@ -8761,7 +8768,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A86" s="1">
         <v>84</v>
       </c>
@@ -8790,7 +8797,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A87" s="1">
         <v>85</v>
       </c>
@@ -8819,7 +8826,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A88" s="1">
         <v>86</v>
       </c>
@@ -8848,7 +8855,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A89" s="1">
         <v>87</v>
       </c>
@@ -8877,7 +8884,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A90" s="1">
         <v>88</v>
       </c>
@@ -8906,7 +8913,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A91" s="1">
         <v>89</v>
       </c>
@@ -8935,7 +8942,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A92" s="1">
         <v>90</v>
       </c>
@@ -8964,7 +8971,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A93" s="1">
         <v>91</v>
       </c>
@@ -8993,7 +9000,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A94" s="1">
         <v>92</v>
       </c>
@@ -9022,7 +9029,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A95" s="1">
         <v>93</v>
       </c>
@@ -9033,7 +9040,7 @@
         <v>9</v>
       </c>
       <c r="D95" t="s">
-        <v>1958</v>
+        <v>1951</v>
       </c>
       <c r="E95" t="s">
         <v>373</v>
@@ -9051,7 +9058,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A96" s="1">
         <v>94</v>
       </c>
@@ -9080,7 +9087,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A97" s="1">
         <v>95</v>
       </c>
@@ -9109,7 +9116,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A98" s="1">
         <v>96</v>
       </c>
@@ -9138,7 +9145,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A99" s="1">
         <v>97</v>
       </c>
@@ -9167,7 +9174,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A100" s="1">
         <v>98</v>
       </c>
@@ -9196,7 +9203,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A101" s="1">
         <v>99</v>
       </c>
@@ -9225,7 +9232,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A102" s="1">
         <v>100</v>
       </c>
@@ -9254,7 +9261,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A103" s="1">
         <v>101</v>
       </c>
@@ -9283,7 +9290,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A104" s="1">
         <v>102</v>
       </c>
@@ -9312,7 +9319,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A105" s="1">
         <v>103</v>
       </c>
@@ -9341,7 +9348,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A106" s="1">
         <v>104</v>
       </c>
@@ -9370,7 +9377,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A107" s="1">
         <v>105</v>
       </c>
@@ -9399,7 +9406,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A108" s="1">
         <v>106</v>
       </c>
@@ -9428,7 +9435,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A109" s="1">
         <v>107</v>
       </c>
@@ -9457,7 +9464,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A110" s="1">
         <v>108</v>
       </c>
@@ -9486,7 +9493,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A111" s="1">
         <v>109</v>
       </c>
@@ -9515,7 +9522,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A112" s="1">
         <v>110</v>
       </c>
@@ -9544,7 +9551,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A113" s="1">
         <v>111</v>
       </c>
@@ -9573,7 +9580,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A114" s="1">
         <v>112</v>
       </c>
@@ -9602,7 +9609,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A115" s="1">
         <v>113</v>
       </c>
@@ -9631,7 +9638,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A116" s="1">
         <v>114</v>
       </c>
@@ -9660,7 +9667,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A117" s="1">
         <v>115</v>
       </c>
@@ -9689,7 +9696,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A118" s="1">
         <v>116</v>
       </c>
@@ -9718,7 +9725,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A119" s="1">
         <v>117</v>
       </c>
@@ -9747,7 +9754,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A120" s="1">
         <v>118</v>
       </c>
@@ -9776,7 +9783,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A121" s="1">
         <v>119</v>
       </c>
@@ -9805,7 +9812,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A122" s="1">
         <v>120</v>
       </c>
@@ -9834,7 +9841,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A123" s="1">
         <v>121</v>
       </c>
@@ -9863,7 +9870,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A124" s="1">
         <v>122</v>
       </c>
@@ -9892,7 +9899,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A125" s="1">
         <v>123</v>
       </c>
@@ -9921,7 +9928,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A126" s="1">
         <v>124</v>
       </c>
@@ -9950,7 +9957,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A127" s="1">
         <v>125</v>
       </c>
@@ -9979,7 +9986,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A128" s="1">
         <v>126</v>
       </c>
@@ -10008,7 +10015,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A129" s="1">
         <v>127</v>
       </c>
@@ -10037,7 +10044,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A130" s="1">
         <v>128</v>
       </c>
@@ -10066,7 +10073,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A131" s="1">
         <v>129</v>
       </c>
@@ -10095,7 +10102,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A132" s="1">
         <v>130</v>
       </c>
@@ -10124,7 +10131,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A133" s="1">
         <v>131</v>
       </c>
@@ -10153,7 +10160,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A134" s="1">
         <v>132</v>
       </c>
@@ -10182,7 +10189,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A135" s="1">
         <v>133</v>
       </c>
@@ -10211,7 +10218,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A136" s="1">
         <v>134</v>
       </c>
@@ -10240,7 +10247,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A137" s="1">
         <v>135</v>
       </c>
@@ -10269,7 +10276,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A138" s="1">
         <v>136</v>
       </c>
@@ -10298,7 +10305,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A139" s="1">
         <v>137</v>
       </c>
@@ -10327,7 +10334,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A140" s="1">
         <v>138</v>
       </c>
@@ -10356,7 +10363,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A141" s="1">
         <v>139</v>
       </c>
@@ -10385,7 +10392,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A142" s="1">
         <v>140</v>
       </c>
@@ -10414,7 +10421,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A143" s="1">
         <v>141</v>
       </c>
@@ -10443,7 +10450,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A144" s="1">
         <v>142</v>
       </c>
@@ -10472,7 +10479,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A145" s="1">
         <v>143</v>
       </c>
@@ -10483,7 +10490,7 @@
         <v>9</v>
       </c>
       <c r="D145" t="s">
-        <v>1959</v>
+        <v>1952</v>
       </c>
       <c r="E145" t="s">
         <v>545</v>
@@ -10501,7 +10508,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A146" s="1">
         <v>144</v>
       </c>
@@ -10530,7 +10537,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A147" s="1">
         <v>145</v>
       </c>
@@ -10559,7 +10566,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A148" s="1">
         <v>146</v>
       </c>
@@ -10588,7 +10595,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A149" s="1">
         <v>147</v>
       </c>
@@ -10617,7 +10624,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A150" s="1">
         <v>148</v>
       </c>
@@ -10646,7 +10653,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A151" s="1">
         <v>149</v>
       </c>
@@ -10675,7 +10682,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A152" s="1">
         <v>150</v>
       </c>
@@ -10704,7 +10711,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A153" s="1">
         <v>151</v>
       </c>
@@ -10733,7 +10740,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A154" s="1">
         <v>152</v>
       </c>
@@ -10762,7 +10769,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A155" s="1">
         <v>153</v>
       </c>
@@ -10791,7 +10798,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A156" s="1">
         <v>154</v>
       </c>
@@ -10820,7 +10827,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A157" s="1">
         <v>155</v>
       </c>
@@ -10849,7 +10856,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A158" s="1">
         <v>156</v>
       </c>
@@ -10878,7 +10885,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A159" s="1">
         <v>157</v>
       </c>
@@ -10907,7 +10914,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A160" s="1">
         <v>158</v>
       </c>
@@ -10936,7 +10943,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A161" s="1">
         <v>159</v>
       </c>
@@ -10965,7 +10972,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A162" s="1">
         <v>160</v>
       </c>
@@ -10994,7 +11001,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="163" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A163" s="1">
         <v>161</v>
       </c>
@@ -11023,7 +11030,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A164" s="1">
         <v>162</v>
       </c>
@@ -11052,7 +11059,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="165" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A165" s="1">
         <v>163</v>
       </c>
@@ -11081,7 +11088,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="166" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A166" s="1">
         <v>164</v>
       </c>
@@ -11110,7 +11117,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="167" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A167" s="1">
         <v>165</v>
       </c>
@@ -11139,7 +11146,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A168" s="1">
         <v>166</v>
       </c>
@@ -11168,7 +11175,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="169" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A169" s="1">
         <v>167</v>
       </c>
@@ -11197,7 +11204,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="170" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A170" s="1">
         <v>168</v>
       </c>
@@ -11226,7 +11233,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A171" s="1">
         <v>169</v>
       </c>
@@ -11255,7 +11262,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A172" s="1">
         <v>170</v>
       </c>
@@ -11284,7 +11291,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A173" s="1">
         <v>171</v>
       </c>
@@ -11313,7 +11320,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="174" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A174" s="1">
         <v>172</v>
       </c>
@@ -11342,7 +11349,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="175" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A175" s="1">
         <v>173</v>
       </c>
@@ -11371,7 +11378,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A176" s="1">
         <v>174</v>
       </c>
@@ -11400,7 +11407,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="177" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A177" s="1">
         <v>175</v>
       </c>
@@ -11429,7 +11436,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="178" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A178" s="1">
         <v>176</v>
       </c>
@@ -11458,7 +11465,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="179" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A179" s="1">
         <v>177</v>
       </c>
@@ -11487,7 +11494,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="180" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A180" s="1">
         <v>178</v>
       </c>
@@ -11516,7 +11523,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="181" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A181" s="1">
         <v>179</v>
       </c>
@@ -11545,7 +11552,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="182" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A182" s="1">
         <v>180</v>
       </c>
@@ -11574,7 +11581,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="183" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A183" s="1">
         <v>181</v>
       </c>
@@ -11603,7 +11610,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="184" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A184" s="1">
         <v>182</v>
       </c>
@@ -11632,7 +11639,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="185" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A185" s="1">
         <v>183</v>
       </c>
@@ -11661,7 +11668,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="186" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A186" s="1">
         <v>184</v>
       </c>
@@ -11690,7 +11697,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="187" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A187" s="1">
         <v>185</v>
       </c>
@@ -11719,7 +11726,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="188" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A188" s="1">
         <v>186</v>
       </c>
@@ -11748,7 +11755,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="189" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A189" s="1">
         <v>187</v>
       </c>
@@ -11777,7 +11784,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="190" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A190" s="1">
         <v>188</v>
       </c>
@@ -11806,7 +11813,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="191" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A191" s="1">
         <v>189</v>
       </c>
@@ -11835,7 +11842,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="192" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A192" s="1">
         <v>190</v>
       </c>
@@ -11864,7 +11871,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A193" s="1">
         <v>191</v>
       </c>
@@ -11893,7 +11900,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A194" s="1">
         <v>192</v>
       </c>
@@ -11922,7 +11929,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="195" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A195" s="1">
         <v>193</v>
       </c>
@@ -11951,7 +11958,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A196" s="1">
         <v>194</v>
       </c>
@@ -11980,7 +11987,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A197" s="1">
         <v>195</v>
       </c>
@@ -12009,7 +12016,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A198" s="1">
         <v>196</v>
       </c>
@@ -12038,7 +12045,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A199" s="1">
         <v>197</v>
       </c>
@@ -12067,7 +12074,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="200" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A200" s="1">
         <v>198</v>
       </c>
@@ -12096,7 +12103,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A201" s="1">
         <v>199</v>
       </c>
@@ -12125,7 +12132,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="202" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A202" s="1">
         <v>200</v>
       </c>
@@ -12154,7 +12161,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="203" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A203" s="1">
         <v>201</v>
       </c>
@@ -12183,7 +12190,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A204" s="1">
         <v>202</v>
       </c>
@@ -12212,7 +12219,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="205" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A205" s="1">
         <v>203</v>
       </c>
@@ -12241,7 +12248,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="206" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A206" s="1">
         <v>204</v>
       </c>
@@ -12252,7 +12259,7 @@
         <v>9</v>
       </c>
       <c r="D206" t="s">
-        <v>1960</v>
+        <v>1953</v>
       </c>
       <c r="E206" t="s">
         <v>748</v>
@@ -12270,7 +12277,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A207" s="1">
         <v>205</v>
       </c>
@@ -12299,7 +12306,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="208" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A208" s="1">
         <v>206</v>
       </c>
@@ -12328,7 +12335,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="209" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="209" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A209" s="1">
         <v>207</v>
       </c>
@@ -12357,7 +12364,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="210" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="210" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A210" s="1">
         <v>208</v>
       </c>
@@ -12386,7 +12393,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="211" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="211" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A211" s="1">
         <v>209</v>
       </c>
@@ -12415,7 +12422,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="212" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="212" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A212" s="1">
         <v>210</v>
       </c>
@@ -12444,7 +12451,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="213" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="213" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A213" s="1">
         <v>211</v>
       </c>
@@ -12473,7 +12480,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="214" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="214" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A214" s="1">
         <v>212</v>
       </c>
@@ -12502,7 +12509,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="215" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="215" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A215" s="1">
         <v>213</v>
       </c>
@@ -12531,7 +12538,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="216" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="216" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A216" s="1">
         <v>214</v>
       </c>
@@ -12560,7 +12567,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="217" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="217" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A217" s="1">
         <v>215</v>
       </c>
@@ -12589,7 +12596,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="218" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="218" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A218" s="1">
         <v>216</v>
       </c>
@@ -12618,7 +12625,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="219" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="219" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A219" s="1">
         <v>217</v>
       </c>
@@ -12647,7 +12654,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="220" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="220" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A220" s="1">
         <v>218</v>
       </c>
@@ -12676,7 +12683,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="221" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="221" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A221" s="1">
         <v>219</v>
       </c>
@@ -12705,7 +12712,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="222" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="222" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A222" s="1">
         <v>220</v>
       </c>
@@ -12734,7 +12741,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="223" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A223" s="1">
         <v>221</v>
       </c>
@@ -12763,7 +12770,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="224" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="224" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A224" s="1">
         <v>222</v>
       </c>
@@ -12792,7 +12799,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="225" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="225" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A225" s="1">
         <v>223</v>
       </c>
@@ -12821,7 +12828,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="226" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="226" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A226" s="1">
         <v>224</v>
       </c>
@@ -12850,7 +12857,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="227" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="227" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A227" s="1">
         <v>225</v>
       </c>
@@ -12861,7 +12868,7 @@
         <v>9</v>
       </c>
       <c r="D227" t="s">
-        <v>1961</v>
+        <v>1954</v>
       </c>
       <c r="E227" t="s">
         <v>819</v>
@@ -12879,7 +12886,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="228" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="228" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A228" s="1">
         <v>226</v>
       </c>
@@ -12908,7 +12915,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="229" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="229" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A229" s="1">
         <v>227</v>
       </c>
@@ -12937,7 +12944,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="230" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="230" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A230" s="1">
         <v>228</v>
       </c>
@@ -12966,7 +12973,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="231" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="231" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A231" s="1">
         <v>229</v>
       </c>
@@ -12995,7 +13002,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="232" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="232" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A232" s="1">
         <v>230</v>
       </c>
@@ -13024,7 +13031,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="233" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="233" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A233" s="1">
         <v>231</v>
       </c>
@@ -13053,7 +13060,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="234" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="234" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A234" s="1">
         <v>232</v>
       </c>
@@ -13082,7 +13089,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="235" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="235" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A235" s="1">
         <v>233</v>
       </c>
@@ -13111,7 +13118,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="236" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="236" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A236" s="1">
         <v>234</v>
       </c>
@@ -13140,7 +13147,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="237" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="237" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A237" s="1">
         <v>235</v>
       </c>
@@ -13169,7 +13176,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="238" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="238" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A238" s="1">
         <v>236</v>
       </c>
@@ -13198,7 +13205,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="239" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="239" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A239" s="1">
         <v>237</v>
       </c>
@@ -13227,7 +13234,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="240" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="240" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A240" s="1">
         <v>238</v>
       </c>
@@ -13256,7 +13263,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="241" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="241" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A241" s="1">
         <v>239</v>
       </c>
@@ -13285,7 +13292,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="242" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="242" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A242" s="1">
         <v>240</v>
       </c>
@@ -13314,7 +13321,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="243" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="243" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A243" s="1">
         <v>241</v>
       </c>
@@ -13343,7 +13350,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="244" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="244" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A244" s="1">
         <v>242</v>
       </c>
@@ -13372,7 +13379,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="245" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="245" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A245" s="1">
         <v>243</v>
       </c>
@@ -13401,7 +13408,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="246" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="246" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A246" s="1">
         <v>244</v>
       </c>
@@ -13430,7 +13437,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="247" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="247" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A247" s="1">
         <v>245</v>
       </c>
@@ -13459,7 +13466,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="248" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="248" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A248" s="1">
         <v>246</v>
       </c>
@@ -13488,7 +13495,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="249" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="249" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A249" s="1">
         <v>247</v>
       </c>
@@ -13517,7 +13524,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="250" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="250" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A250" s="1">
         <v>248</v>
       </c>
@@ -13546,7 +13553,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="251" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="251" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A251" s="1">
         <v>249</v>
       </c>
@@ -13575,7 +13582,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="252" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="252" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A252" s="1">
         <v>250</v>
       </c>
@@ -13604,7 +13611,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="253" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="253" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A253" s="1">
         <v>251</v>
       </c>
@@ -13633,7 +13640,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="254" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="254" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A254" s="1">
         <v>252</v>
       </c>
@@ -13662,7 +13669,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="255" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="255" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A255" s="1">
         <v>253</v>
       </c>
@@ -13691,7 +13698,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="256" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="256" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A256" s="1">
         <v>254</v>
       </c>
@@ -13720,7 +13727,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="257" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="257" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A257" s="1">
         <v>255</v>
       </c>
@@ -13749,7 +13756,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="258" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="258" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A258" s="1">
         <v>256</v>
       </c>
@@ -13778,7 +13785,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="259" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="259" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A259" s="1">
         <v>257</v>
       </c>
@@ -13807,7 +13814,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="260" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="260" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A260" s="1">
         <v>258</v>
       </c>
@@ -13836,7 +13843,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="261" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="261" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A261" s="1">
         <v>259</v>
       </c>
@@ -13865,7 +13872,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="262" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="262" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A262" s="1">
         <v>260</v>
       </c>
@@ -13894,7 +13901,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="263" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="263" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A263" s="1">
         <v>261</v>
       </c>
@@ -13923,7 +13930,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="264" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="264" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A264" s="1">
         <v>262</v>
       </c>
@@ -13952,7 +13959,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="265" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="265" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A265" s="1">
         <v>263</v>
       </c>
@@ -13981,7 +13988,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="266" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="266" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A266" s="1">
         <v>264</v>
       </c>
@@ -14010,7 +14017,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="267" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="267" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A267" s="1">
         <v>265</v>
       </c>
@@ -14039,7 +14046,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="268" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="268" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A268" s="1">
         <v>266</v>
       </c>
@@ -14068,7 +14075,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="269" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="269" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A269" s="1">
         <v>267</v>
       </c>
@@ -14097,7 +14104,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="270" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="270" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A270" s="1">
         <v>268</v>
       </c>
@@ -14126,7 +14133,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="271" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="271" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A271" s="1">
         <v>269</v>
       </c>
@@ -14155,7 +14162,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="272" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="272" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A272" s="1">
         <v>270</v>
       </c>
@@ -14184,7 +14191,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="273" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="273" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A273" s="1">
         <v>271</v>
       </c>
@@ -14213,7 +14220,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="274" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="274" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A274" s="1">
         <v>272</v>
       </c>
@@ -14242,7 +14249,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="275" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="275" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A275" s="1">
         <v>273</v>
       </c>
@@ -14271,7 +14278,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="276" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="276" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A276" s="1">
         <v>274</v>
       </c>
@@ -14300,7 +14307,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="277" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="277" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A277" s="1">
         <v>275</v>
       </c>
@@ -14329,7 +14336,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="278" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="278" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A278" s="1">
         <v>276</v>
       </c>
@@ -14358,7 +14365,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="279" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="279" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A279" s="1">
         <v>277</v>
       </c>
@@ -14387,7 +14394,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="280" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="280" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A280" s="1">
         <v>278</v>
       </c>
@@ -14416,7 +14423,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="281" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="281" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A281" s="1">
         <v>279</v>
       </c>
@@ -14445,7 +14452,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="282" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="282" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A282" s="1">
         <v>280</v>
       </c>
@@ -14474,7 +14481,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="283" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="283" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A283" s="1">
         <v>281</v>
       </c>
@@ -14503,7 +14510,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="284" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="284" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A284" s="1">
         <v>282</v>
       </c>
@@ -14532,7 +14539,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="285" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="285" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A285" s="1">
         <v>283</v>
       </c>
@@ -14561,7 +14568,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="286" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="286" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A286" s="1">
         <v>284</v>
       </c>
@@ -14590,7 +14597,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="287" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="287" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A287" s="1">
         <v>285</v>
       </c>
@@ -14619,7 +14626,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="288" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="288" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A288" s="1">
         <v>286</v>
       </c>
@@ -14648,7 +14655,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="289" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="289" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A289" s="1">
         <v>287</v>
       </c>
@@ -14677,7 +14684,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="290" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="290" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A290" s="1">
         <v>288</v>
       </c>
@@ -14706,7 +14713,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="291" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="291" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A291" s="1">
         <v>289</v>
       </c>
@@ -14735,7 +14742,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="292" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="292" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A292" s="1">
         <v>290</v>
       </c>
@@ -14764,7 +14771,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="293" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="293" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A293" s="1">
         <v>291</v>
       </c>
@@ -14793,7 +14800,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="294" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="294" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A294" s="1">
         <v>292</v>
       </c>
@@ -14822,7 +14829,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="295" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="295" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A295" s="1">
         <v>293</v>
       </c>
@@ -14851,7 +14858,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="296" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="296" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A296" s="1">
         <v>294</v>
       </c>
@@ -14880,7 +14887,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="297" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="297" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A297" s="1">
         <v>295</v>
       </c>
@@ -14909,7 +14916,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="298" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="298" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A298" s="1">
         <v>296</v>
       </c>
@@ -14938,7 +14945,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="299" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="299" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A299" s="1">
         <v>297</v>
       </c>
@@ -14967,7 +14974,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="300" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="300" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A300" s="1">
         <v>298</v>
       </c>
@@ -14996,7 +15003,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="301" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="301" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A301" s="1">
         <v>299</v>
       </c>
@@ -15025,7 +15032,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="302" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="302" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A302" s="1">
         <v>300</v>
       </c>
@@ -15054,7 +15061,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="303" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="303" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A303" s="1">
         <v>301</v>
       </c>
@@ -15083,7 +15090,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="304" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="304" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A304" s="1">
         <v>302</v>
       </c>
@@ -15112,7 +15119,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="305" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="305" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A305" s="1">
         <v>303</v>
       </c>
@@ -15141,7 +15148,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="306" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="306" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A306" s="1">
         <v>304</v>
       </c>
@@ -15170,7 +15177,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="307" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="307" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A307" s="1">
         <v>305</v>
       </c>
@@ -15199,7 +15206,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="308" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="308" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A308" s="1">
         <v>306</v>
       </c>
@@ -15228,7 +15235,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="309" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="309" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A309" s="1">
         <v>307</v>
       </c>
@@ -15257,7 +15264,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="310" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="310" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A310" s="1">
         <v>308</v>
       </c>
@@ -15286,7 +15293,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="311" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="311" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A311" s="1">
         <v>309</v>
       </c>
@@ -15315,7 +15322,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="312" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="312" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A312" s="1">
         <v>310</v>
       </c>
@@ -15344,7 +15351,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="313" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="313" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A313" s="1">
         <v>311</v>
       </c>
@@ -15373,7 +15380,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="314" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="314" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A314" s="1">
         <v>312</v>
       </c>
@@ -15402,7 +15409,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="315" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="315" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A315" s="1">
         <v>313</v>
       </c>
@@ -15431,7 +15438,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="316" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="316" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A316" s="1">
         <v>314</v>
       </c>
@@ -15460,7 +15467,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="317" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="317" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A317" s="1">
         <v>315</v>
       </c>
@@ -15489,7 +15496,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="318" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="318" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A318" s="1">
         <v>316</v>
       </c>
@@ -15518,7 +15525,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="319" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="319" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A319" s="1">
         <v>317</v>
       </c>
@@ -15547,7 +15554,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="320" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="320" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A320" s="1">
         <v>318</v>
       </c>
@@ -15576,7 +15583,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="321" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="321" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A321" s="1">
         <v>319</v>
       </c>
@@ -15605,7 +15612,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="322" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="322" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A322" s="1">
         <v>320</v>
       </c>
@@ -15634,7 +15641,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="323" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="323" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A323" s="1">
         <v>321</v>
       </c>
@@ -15663,7 +15670,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="324" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="324" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A324" s="1">
         <v>322</v>
       </c>
@@ -15692,7 +15699,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="325" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="325" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A325" s="1">
         <v>323</v>
       </c>
@@ -15721,7 +15728,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="326" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="326" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A326" s="1">
         <v>324</v>
       </c>
@@ -15750,7 +15757,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="327" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="327" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A327" s="1">
         <v>325</v>
       </c>
@@ -15761,7 +15768,7 @@
         <v>9</v>
       </c>
       <c r="D327" t="s">
-        <v>1962</v>
+        <v>1955</v>
       </c>
       <c r="E327" t="s">
         <v>1168</v>
@@ -15776,7 +15783,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="328" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="328" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A328" s="1">
         <v>326</v>
       </c>
@@ -15802,7 +15809,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="329" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="329" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A329" s="1">
         <v>327</v>
       </c>
@@ -15813,7 +15820,7 @@
         <v>9</v>
       </c>
       <c r="D329" t="s">
-        <v>1963</v>
+        <v>1956</v>
       </c>
       <c r="E329" t="s">
         <v>1175</v>
@@ -15831,7 +15838,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="330" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="330" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A330" s="1">
         <v>328</v>
       </c>
@@ -15860,7 +15867,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="331" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="331" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A331" s="1">
         <v>329</v>
       </c>
@@ -15889,7 +15896,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="332" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="332" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A332" s="1">
         <v>330</v>
       </c>
@@ -15918,7 +15925,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="333" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="333" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A333" s="1">
         <v>331</v>
       </c>
@@ -15947,7 +15954,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="334" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="334" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A334" s="1">
         <v>332</v>
       </c>
@@ -15976,7 +15983,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="335" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="335" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A335" s="1">
         <v>333</v>
       </c>
@@ -16005,7 +16012,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="336" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="336" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A336" s="1">
         <v>334</v>
       </c>
@@ -16034,7 +16041,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="337" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="337" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A337" s="1">
         <v>335</v>
       </c>
@@ -16063,7 +16070,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="338" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="338" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A338" s="1">
         <v>336</v>
       </c>
@@ -16092,7 +16099,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="339" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="339" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A339" s="1">
         <v>337</v>
       </c>
@@ -16121,7 +16128,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="340" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="340" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A340" s="1">
         <v>338</v>
       </c>
@@ -16150,7 +16157,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="341" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="341" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A341" s="1">
         <v>339</v>
       </c>
@@ -16179,7 +16186,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="342" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="342" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A342" s="1">
         <v>340</v>
       </c>
@@ -16208,7 +16215,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="343" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="343" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A343" s="1">
         <v>341</v>
       </c>
@@ -16237,7 +16244,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="344" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="344" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A344" s="1">
         <v>342</v>
       </c>
@@ -16266,7 +16273,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="345" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="345" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A345" s="1">
         <v>343</v>
       </c>
@@ -16295,7 +16302,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="346" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="346" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A346" s="1">
         <v>344</v>
       </c>
@@ -16324,7 +16331,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="347" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="347" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A347" s="1">
         <v>345</v>
       </c>
@@ -16353,7 +16360,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="348" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="348" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A348" s="1">
         <v>346</v>
       </c>
@@ -16382,7 +16389,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="349" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="349" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A349" s="1">
         <v>347</v>
       </c>
@@ -16411,7 +16418,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="350" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="350" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A350" s="1">
         <v>348</v>
       </c>
@@ -16422,7 +16429,7 @@
         <v>9</v>
       </c>
       <c r="D350" t="s">
-        <v>1964</v>
+        <v>1957</v>
       </c>
       <c r="E350" t="s">
         <v>1260</v>
@@ -16440,7 +16447,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="351" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="351" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A351" s="1">
         <v>349</v>
       </c>
@@ -16469,7 +16476,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="352" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="352" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A352" s="1">
         <v>350</v>
       </c>
@@ -16498,7 +16505,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="353" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="353" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A353" s="1">
         <v>351</v>
       </c>
@@ -16527,7 +16534,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="354" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="354" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A354" s="1">
         <v>352</v>
       </c>
@@ -16556,7 +16563,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="355" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="355" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A355" s="1">
         <v>353</v>
       </c>
@@ -16585,7 +16592,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="356" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="356" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A356" s="1">
         <v>354</v>
       </c>
@@ -16614,7 +16621,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="357" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="357" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A357" s="1">
         <v>355</v>
       </c>
@@ -16643,7 +16650,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="358" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="358" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A358" s="1">
         <v>356</v>
       </c>
@@ -16654,16 +16661,16 @@
         <v>9</v>
       </c>
       <c r="D358" t="s">
+        <v>1961</v>
+      </c>
+      <c r="E358" t="s">
         <v>1291</v>
       </c>
-      <c r="E358" t="s">
+      <c r="F358" t="s">
         <v>1292</v>
       </c>
-      <c r="F358" t="s">
+      <c r="G358" t="s">
         <v>1293</v>
-      </c>
-      <c r="G358" t="s">
-        <v>1294</v>
       </c>
       <c r="H358" t="s">
         <v>1187</v>
@@ -16672,7 +16679,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="359" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="359" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A359" s="1">
         <v>357</v>
       </c>
@@ -16683,25 +16690,25 @@
         <v>9</v>
       </c>
       <c r="D359" t="s">
+        <v>1964</v>
+      </c>
+      <c r="E359" t="s">
+        <v>1294</v>
+      </c>
+      <c r="F359" t="s">
         <v>1295</v>
       </c>
-      <c r="E359" t="s">
+      <c r="G359" t="s">
         <v>1296</v>
       </c>
-      <c r="F359" t="s">
+      <c r="H359" t="s">
         <v>1297</v>
       </c>
-      <c r="G359" t="s">
-        <v>1298</v>
-      </c>
-      <c r="H359" t="s">
-        <v>1299</v>
-      </c>
       <c r="I359" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="360" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="360" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A360" s="1">
         <v>358</v>
       </c>
@@ -16712,16 +16719,16 @@
         <v>9</v>
       </c>
       <c r="D360" t="s">
+        <v>1298</v>
+      </c>
+      <c r="E360" t="s">
+        <v>1299</v>
+      </c>
+      <c r="F360" t="s">
         <v>1300</v>
       </c>
-      <c r="E360" t="s">
+      <c r="G360" t="s">
         <v>1301</v>
-      </c>
-      <c r="F360" t="s">
-        <v>1302</v>
-      </c>
-      <c r="G360" t="s">
-        <v>1303</v>
       </c>
       <c r="H360" t="s">
         <v>1187</v>
@@ -16730,7 +16737,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="361" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="361" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A361" s="1">
         <v>359</v>
       </c>
@@ -16741,25 +16748,25 @@
         <v>9</v>
       </c>
       <c r="D361" t="s">
+        <v>1302</v>
+      </c>
+      <c r="E361" t="s">
+        <v>1303</v>
+      </c>
+      <c r="F361" t="s">
         <v>1304</v>
       </c>
-      <c r="E361" t="s">
+      <c r="G361" t="s">
         <v>1305</v>
       </c>
-      <c r="F361" t="s">
+      <c r="H361" t="s">
         <v>1306</v>
       </c>
-      <c r="G361" t="s">
-        <v>1307</v>
-      </c>
-      <c r="H361" t="s">
-        <v>1308</v>
-      </c>
       <c r="I361" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="362" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="362" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A362" s="1">
         <v>360</v>
       </c>
@@ -16770,25 +16777,25 @@
         <v>9</v>
       </c>
       <c r="D362" t="s">
+        <v>1307</v>
+      </c>
+      <c r="E362" t="s">
+        <v>1308</v>
+      </c>
+      <c r="F362" t="s">
         <v>1309</v>
       </c>
-      <c r="E362" t="s">
+      <c r="G362" t="s">
         <v>1310</v>
       </c>
-      <c r="F362" t="s">
-        <v>1311</v>
-      </c>
-      <c r="G362" t="s">
-        <v>1312</v>
-      </c>
       <c r="H362" t="s">
-        <v>1308</v>
+        <v>1306</v>
       </c>
       <c r="I362" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="363" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="363" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A363" s="1">
         <v>361</v>
       </c>
@@ -16799,25 +16806,25 @@
         <v>9</v>
       </c>
       <c r="D363" t="s">
+        <v>1311</v>
+      </c>
+      <c r="E363" t="s">
+        <v>1312</v>
+      </c>
+      <c r="F363" t="s">
         <v>1313</v>
       </c>
-      <c r="E363" t="s">
+      <c r="G363" t="s">
         <v>1314</v>
       </c>
-      <c r="F363" t="s">
+      <c r="H363" t="s">
         <v>1315</v>
       </c>
-      <c r="G363" t="s">
-        <v>1316</v>
-      </c>
-      <c r="H363" t="s">
-        <v>1317</v>
-      </c>
       <c r="I363" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="364" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="364" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A364" s="1">
         <v>362</v>
       </c>
@@ -16828,25 +16835,25 @@
         <v>9</v>
       </c>
       <c r="D364" t="s">
+        <v>1316</v>
+      </c>
+      <c r="E364" t="s">
+        <v>1317</v>
+      </c>
+      <c r="F364" t="s">
         <v>1318</v>
       </c>
-      <c r="E364" t="s">
+      <c r="G364" t="s">
         <v>1319</v>
       </c>
-      <c r="F364" t="s">
-        <v>1320</v>
-      </c>
-      <c r="G364" t="s">
-        <v>1321</v>
-      </c>
       <c r="H364" t="s">
-        <v>1317</v>
+        <v>1315</v>
       </c>
       <c r="I364" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="365" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="365" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A365" s="1">
         <v>363</v>
       </c>
@@ -16857,25 +16864,25 @@
         <v>9</v>
       </c>
       <c r="D365" t="s">
+        <v>1320</v>
+      </c>
+      <c r="E365" t="s">
+        <v>1321</v>
+      </c>
+      <c r="F365" t="s">
         <v>1322</v>
       </c>
-      <c r="E365" t="s">
+      <c r="G365" t="s">
         <v>1323</v>
       </c>
-      <c r="F365" t="s">
+      <c r="H365" t="s">
         <v>1324</v>
       </c>
-      <c r="G365" t="s">
-        <v>1325</v>
-      </c>
-      <c r="H365" t="s">
-        <v>1326</v>
-      </c>
       <c r="I365" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="366" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="366" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A366" s="1">
         <v>364</v>
       </c>
@@ -16886,25 +16893,25 @@
         <v>9</v>
       </c>
       <c r="D366" t="s">
+        <v>1325</v>
+      </c>
+      <c r="E366" t="s">
+        <v>1326</v>
+      </c>
+      <c r="F366" t="s">
         <v>1327</v>
       </c>
-      <c r="E366" t="s">
+      <c r="G366" t="s">
         <v>1328</v>
       </c>
-      <c r="F366" t="s">
+      <c r="H366" t="s">
         <v>1329</v>
       </c>
-      <c r="G366" t="s">
-        <v>1330</v>
-      </c>
-      <c r="H366" t="s">
-        <v>1331</v>
-      </c>
       <c r="I366" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="367" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="367" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A367" s="1">
         <v>365</v>
       </c>
@@ -16915,25 +16922,25 @@
         <v>9</v>
       </c>
       <c r="D367" t="s">
+        <v>1330</v>
+      </c>
+      <c r="E367" t="s">
+        <v>1331</v>
+      </c>
+      <c r="F367" t="s">
         <v>1332</v>
       </c>
-      <c r="E367" t="s">
+      <c r="G367" t="s">
         <v>1333</v>
       </c>
-      <c r="F367" t="s">
+      <c r="H367" t="s">
         <v>1334</v>
       </c>
-      <c r="G367" t="s">
-        <v>1335</v>
-      </c>
-      <c r="H367" t="s">
-        <v>1336</v>
-      </c>
       <c r="I367" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="368" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="368" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A368" s="1">
         <v>366</v>
       </c>
@@ -16944,25 +16951,25 @@
         <v>9</v>
       </c>
       <c r="D368" t="s">
+        <v>1335</v>
+      </c>
+      <c r="E368" t="s">
+        <v>1336</v>
+      </c>
+      <c r="F368" t="s">
         <v>1337</v>
       </c>
-      <c r="E368" t="s">
+      <c r="G368" t="s">
         <v>1338</v>
       </c>
-      <c r="F368" t="s">
+      <c r="H368" t="s">
         <v>1339</v>
       </c>
-      <c r="G368" t="s">
-        <v>1340</v>
-      </c>
-      <c r="H368" t="s">
-        <v>1341</v>
-      </c>
       <c r="I368" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="369" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="369" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A369" s="1">
         <v>367</v>
       </c>
@@ -16973,25 +16980,25 @@
         <v>9</v>
       </c>
       <c r="D369" t="s">
+        <v>1340</v>
+      </c>
+      <c r="E369" t="s">
+        <v>1341</v>
+      </c>
+      <c r="F369" t="s">
         <v>1342</v>
       </c>
-      <c r="E369" t="s">
+      <c r="G369" t="s">
         <v>1343</v>
       </c>
-      <c r="F369" t="s">
+      <c r="H369" t="s">
         <v>1344</v>
       </c>
-      <c r="G369" t="s">
-        <v>1345</v>
-      </c>
-      <c r="H369" t="s">
-        <v>1346</v>
-      </c>
       <c r="I369" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="370" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="370" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A370" s="1">
         <v>368</v>
       </c>
@@ -17002,25 +17009,25 @@
         <v>9</v>
       </c>
       <c r="D370" t="s">
+        <v>1345</v>
+      </c>
+      <c r="E370" t="s">
+        <v>1346</v>
+      </c>
+      <c r="F370" t="s">
         <v>1347</v>
       </c>
-      <c r="E370" t="s">
+      <c r="G370" t="s">
         <v>1348</v>
       </c>
-      <c r="F370" t="s">
-        <v>1349</v>
-      </c>
-      <c r="G370" t="s">
-        <v>1350</v>
-      </c>
       <c r="H370" t="s">
-        <v>1331</v>
+        <v>1329</v>
       </c>
       <c r="I370" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="371" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="371" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A371" s="1">
         <v>369</v>
       </c>
@@ -17031,25 +17038,25 @@
         <v>9</v>
       </c>
       <c r="D371" t="s">
+        <v>1349</v>
+      </c>
+      <c r="E371" t="s">
+        <v>1350</v>
+      </c>
+      <c r="F371" t="s">
         <v>1351</v>
       </c>
-      <c r="E371" t="s">
+      <c r="G371" t="s">
         <v>1352</v>
       </c>
-      <c r="F371" t="s">
-        <v>1353</v>
-      </c>
-      <c r="G371" t="s">
-        <v>1354</v>
-      </c>
       <c r="H371" t="s">
-        <v>1331</v>
+        <v>1329</v>
       </c>
       <c r="I371" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="372" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="372" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A372" s="1">
         <v>370</v>
       </c>
@@ -17060,25 +17067,25 @@
         <v>9</v>
       </c>
       <c r="D372" t="s">
+        <v>1353</v>
+      </c>
+      <c r="E372" t="s">
+        <v>1354</v>
+      </c>
+      <c r="F372" t="s">
         <v>1355</v>
       </c>
-      <c r="E372" t="s">
+      <c r="G372" t="s">
         <v>1356</v>
       </c>
-      <c r="F372" t="s">
+      <c r="H372" t="s">
         <v>1357</v>
       </c>
-      <c r="G372" t="s">
-        <v>1358</v>
-      </c>
-      <c r="H372" t="s">
-        <v>1359</v>
-      </c>
       <c r="I372" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="373" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="373" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A373" s="1">
         <v>371</v>
       </c>
@@ -17089,25 +17096,25 @@
         <v>9</v>
       </c>
       <c r="D373" t="s">
+        <v>1358</v>
+      </c>
+      <c r="E373" t="s">
+        <v>1359</v>
+      </c>
+      <c r="F373" t="s">
         <v>1360</v>
       </c>
-      <c r="E373" t="s">
+      <c r="G373" t="s">
         <v>1361</v>
       </c>
-      <c r="F373" t="s">
+      <c r="H373" t="s">
         <v>1362</v>
       </c>
-      <c r="G373" t="s">
-        <v>1363</v>
-      </c>
-      <c r="H373" t="s">
-        <v>1364</v>
-      </c>
       <c r="I373" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="374" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="374" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A374" s="1">
         <v>372</v>
       </c>
@@ -17118,25 +17125,25 @@
         <v>9</v>
       </c>
       <c r="D374" t="s">
+        <v>1363</v>
+      </c>
+      <c r="E374" t="s">
+        <v>1364</v>
+      </c>
+      <c r="F374" t="s">
         <v>1365</v>
       </c>
-      <c r="E374" t="s">
+      <c r="G374" t="s">
         <v>1366</v>
       </c>
-      <c r="F374" t="s">
+      <c r="H374" t="s">
         <v>1367</v>
       </c>
-      <c r="G374" t="s">
-        <v>1368</v>
-      </c>
-      <c r="H374" t="s">
-        <v>1369</v>
-      </c>
       <c r="I374" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="375" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="375" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A375" s="1">
         <v>373</v>
       </c>
@@ -17147,25 +17154,25 @@
         <v>9</v>
       </c>
       <c r="D375" t="s">
+        <v>1368</v>
+      </c>
+      <c r="E375" t="s">
+        <v>1369</v>
+      </c>
+      <c r="F375" t="s">
         <v>1370</v>
       </c>
-      <c r="E375" t="s">
+      <c r="G375" t="s">
         <v>1371</v>
       </c>
-      <c r="F375" t="s">
-        <v>1372</v>
-      </c>
-      <c r="G375" t="s">
-        <v>1373</v>
-      </c>
       <c r="H375" t="s">
-        <v>1369</v>
+        <v>1367</v>
       </c>
       <c r="I375" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="376" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="376" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A376" s="1">
         <v>374</v>
       </c>
@@ -17176,25 +17183,25 @@
         <v>9</v>
       </c>
       <c r="D376" t="s">
+        <v>1372</v>
+      </c>
+      <c r="E376" t="s">
+        <v>1373</v>
+      </c>
+      <c r="F376" t="s">
         <v>1374</v>
       </c>
-      <c r="E376" t="s">
+      <c r="G376" t="s">
         <v>1375</v>
       </c>
-      <c r="F376" t="s">
-        <v>1376</v>
-      </c>
-      <c r="G376" t="s">
-        <v>1377</v>
-      </c>
       <c r="H376" t="s">
-        <v>1369</v>
+        <v>1367</v>
       </c>
       <c r="I376" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="377" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="377" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A377" s="1">
         <v>375</v>
       </c>
@@ -17205,25 +17212,25 @@
         <v>9</v>
       </c>
       <c r="D377" t="s">
+        <v>1376</v>
+      </c>
+      <c r="E377" t="s">
+        <v>1377</v>
+      </c>
+      <c r="F377" t="s">
         <v>1378</v>
       </c>
-      <c r="E377" t="s">
+      <c r="G377" t="s">
         <v>1379</v>
       </c>
-      <c r="F377" t="s">
-        <v>1380</v>
-      </c>
-      <c r="G377" t="s">
-        <v>1381</v>
-      </c>
       <c r="H377" t="s">
-        <v>1369</v>
+        <v>1367</v>
       </c>
       <c r="I377" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="378" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="378" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A378" s="1">
         <v>376</v>
       </c>
@@ -17234,25 +17241,25 @@
         <v>9</v>
       </c>
       <c r="D378" t="s">
+        <v>1380</v>
+      </c>
+      <c r="E378" t="s">
+        <v>1381</v>
+      </c>
+      <c r="F378" t="s">
         <v>1382</v>
       </c>
-      <c r="E378" t="s">
+      <c r="G378" t="s">
         <v>1383</v>
       </c>
-      <c r="F378" t="s">
-        <v>1384</v>
-      </c>
-      <c r="G378" t="s">
-        <v>1385</v>
-      </c>
       <c r="H378" t="s">
-        <v>1369</v>
+        <v>1367</v>
       </c>
       <c r="I378" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="379" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="379" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A379" s="1">
         <v>377</v>
       </c>
@@ -17263,25 +17270,25 @@
         <v>9</v>
       </c>
       <c r="D379" t="s">
+        <v>1384</v>
+      </c>
+      <c r="E379" t="s">
+        <v>1385</v>
+      </c>
+      <c r="F379" t="s">
         <v>1386</v>
       </c>
-      <c r="E379" t="s">
+      <c r="G379" t="s">
         <v>1387</v>
       </c>
-      <c r="F379" t="s">
-        <v>1388</v>
-      </c>
-      <c r="G379" t="s">
-        <v>1389</v>
-      </c>
       <c r="H379" t="s">
-        <v>1369</v>
+        <v>1367</v>
       </c>
       <c r="I379" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="380" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="380" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A380" s="1">
         <v>378</v>
       </c>
@@ -17292,25 +17299,25 @@
         <v>9</v>
       </c>
       <c r="D380" t="s">
+        <v>1388</v>
+      </c>
+      <c r="E380" t="s">
+        <v>1389</v>
+      </c>
+      <c r="F380" t="s">
         <v>1390</v>
       </c>
-      <c r="E380" t="s">
+      <c r="G380" t="s">
         <v>1391</v>
       </c>
-      <c r="F380" t="s">
-        <v>1392</v>
-      </c>
-      <c r="G380" t="s">
-        <v>1393</v>
-      </c>
       <c r="H380" t="s">
-        <v>1369</v>
+        <v>1367</v>
       </c>
       <c r="I380" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="381" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="381" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A381" s="1">
         <v>379</v>
       </c>
@@ -17321,25 +17328,25 @@
         <v>9</v>
       </c>
       <c r="D381" t="s">
+        <v>1392</v>
+      </c>
+      <c r="E381" t="s">
+        <v>1393</v>
+      </c>
+      <c r="F381" t="s">
         <v>1394</v>
       </c>
-      <c r="E381" t="s">
+      <c r="G381" t="s">
         <v>1395</v>
       </c>
-      <c r="F381" t="s">
-        <v>1396</v>
-      </c>
-      <c r="G381" t="s">
-        <v>1397</v>
-      </c>
       <c r="H381" t="s">
-        <v>1369</v>
+        <v>1367</v>
       </c>
       <c r="I381" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="382" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="382" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A382" s="1">
         <v>380</v>
       </c>
@@ -17350,25 +17357,25 @@
         <v>9</v>
       </c>
       <c r="D382" t="s">
+        <v>1396</v>
+      </c>
+      <c r="E382" t="s">
+        <v>1397</v>
+      </c>
+      <c r="F382" t="s">
         <v>1398</v>
       </c>
-      <c r="E382" t="s">
+      <c r="G382" t="s">
         <v>1399</v>
       </c>
-      <c r="F382" t="s">
-        <v>1400</v>
-      </c>
-      <c r="G382" t="s">
-        <v>1401</v>
-      </c>
       <c r="H382" t="s">
-        <v>1369</v>
+        <v>1367</v>
       </c>
       <c r="I382" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="383" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="383" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A383" s="1">
         <v>381</v>
       </c>
@@ -17379,25 +17386,25 @@
         <v>9</v>
       </c>
       <c r="D383" t="s">
+        <v>1400</v>
+      </c>
+      <c r="E383" t="s">
+        <v>1401</v>
+      </c>
+      <c r="F383" t="s">
         <v>1402</v>
       </c>
-      <c r="E383" t="s">
+      <c r="G383" t="s">
         <v>1403</v>
       </c>
-      <c r="F383" t="s">
-        <v>1404</v>
-      </c>
-      <c r="G383" t="s">
-        <v>1405</v>
-      </c>
       <c r="H383" t="s">
-        <v>1369</v>
+        <v>1367</v>
       </c>
       <c r="I383" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="384" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="384" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A384" s="1">
         <v>382</v>
       </c>
@@ -17408,25 +17415,25 @@
         <v>9</v>
       </c>
       <c r="D384" t="s">
+        <v>1404</v>
+      </c>
+      <c r="E384" t="s">
+        <v>1405</v>
+      </c>
+      <c r="F384" t="s">
         <v>1406</v>
       </c>
-      <c r="E384" t="s">
+      <c r="G384" t="s">
         <v>1407</v>
       </c>
-      <c r="F384" t="s">
+      <c r="H384" t="s">
         <v>1408</v>
       </c>
-      <c r="G384" t="s">
-        <v>1409</v>
-      </c>
-      <c r="H384" t="s">
-        <v>1410</v>
-      </c>
       <c r="I384" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="385" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="385" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A385" s="1">
         <v>383</v>
       </c>
@@ -17437,16 +17444,16 @@
         <v>9</v>
       </c>
       <c r="D385" t="s">
+        <v>1409</v>
+      </c>
+      <c r="E385" t="s">
+        <v>1410</v>
+      </c>
+      <c r="F385" t="s">
         <v>1411</v>
       </c>
-      <c r="E385" t="s">
+      <c r="G385" t="s">
         <v>1412</v>
-      </c>
-      <c r="F385" t="s">
-        <v>1413</v>
-      </c>
-      <c r="G385" t="s">
-        <v>1414</v>
       </c>
       <c r="H385" t="s">
         <v>1167</v>
@@ -17455,7 +17462,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="386" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="386" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A386" s="1">
         <v>384</v>
       </c>
@@ -17466,25 +17473,25 @@
         <v>9</v>
       </c>
       <c r="D386" t="s">
+        <v>1413</v>
+      </c>
+      <c r="E386" t="s">
+        <v>1414</v>
+      </c>
+      <c r="F386" t="s">
         <v>1415</v>
       </c>
-      <c r="E386" t="s">
+      <c r="G386" t="s">
         <v>1416</v>
       </c>
-      <c r="F386" t="s">
+      <c r="H386" t="s">
         <v>1417</v>
       </c>
-      <c r="G386" t="s">
-        <v>1418</v>
-      </c>
-      <c r="H386" t="s">
-        <v>1419</v>
-      </c>
       <c r="I386" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="387" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="387" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A387" s="1">
         <v>385</v>
       </c>
@@ -17495,16 +17502,16 @@
         <v>9</v>
       </c>
       <c r="D387" t="s">
+        <v>1958</v>
+      </c>
+      <c r="E387" t="s">
+        <v>1418</v>
+      </c>
+      <c r="F387" t="s">
+        <v>1419</v>
+      </c>
+      <c r="G387" t="s">
         <v>1420</v>
-      </c>
-      <c r="E387" t="s">
-        <v>1421</v>
-      </c>
-      <c r="F387" t="s">
-        <v>1422</v>
-      </c>
-      <c r="G387" t="s">
-        <v>1423</v>
       </c>
       <c r="H387" t="s">
         <v>22</v>
@@ -17513,7 +17520,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="388" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="388" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A388" s="1">
         <v>386</v>
       </c>
@@ -17524,16 +17531,16 @@
         <v>9</v>
       </c>
       <c r="D388" t="s">
+        <v>1421</v>
+      </c>
+      <c r="E388" t="s">
+        <v>1422</v>
+      </c>
+      <c r="F388" t="s">
+        <v>1423</v>
+      </c>
+      <c r="G388" t="s">
         <v>1424</v>
-      </c>
-      <c r="E388" t="s">
-        <v>1425</v>
-      </c>
-      <c r="F388" t="s">
-        <v>1426</v>
-      </c>
-      <c r="G388" t="s">
-        <v>1427</v>
       </c>
       <c r="H388" t="s">
         <v>1187</v>
@@ -17542,7 +17549,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="389" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="389" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A389" s="1">
         <v>387</v>
       </c>
@@ -17553,16 +17560,16 @@
         <v>9</v>
       </c>
       <c r="D389" t="s">
+        <v>1425</v>
+      </c>
+      <c r="E389" t="s">
+        <v>1426</v>
+      </c>
+      <c r="F389" t="s">
+        <v>1427</v>
+      </c>
+      <c r="G389" t="s">
         <v>1428</v>
-      </c>
-      <c r="E389" t="s">
-        <v>1429</v>
-      </c>
-      <c r="F389" t="s">
-        <v>1430</v>
-      </c>
-      <c r="G389" t="s">
-        <v>1431</v>
       </c>
       <c r="H389" t="s">
         <v>1187</v>
@@ -17571,7 +17578,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="390" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="390" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A390" s="1">
         <v>388</v>
       </c>
@@ -17582,16 +17589,16 @@
         <v>9</v>
       </c>
       <c r="D390" t="s">
-        <v>1432</v>
+        <v>1429</v>
       </c>
       <c r="E390" t="s">
-        <v>1433</v>
+        <v>1430</v>
       </c>
       <c r="F390" t="s">
         <v>391</v>
       </c>
       <c r="G390" t="s">
-        <v>1434</v>
+        <v>1431</v>
       </c>
       <c r="H390" t="s">
         <v>1187</v>
@@ -17600,7 +17607,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="391" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="391" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A391" s="1">
         <v>389</v>
       </c>
@@ -17611,16 +17618,16 @@
         <v>9</v>
       </c>
       <c r="D391" t="s">
+        <v>1432</v>
+      </c>
+      <c r="E391" t="s">
+        <v>1433</v>
+      </c>
+      <c r="F391" t="s">
+        <v>1434</v>
+      </c>
+      <c r="G391" t="s">
         <v>1435</v>
-      </c>
-      <c r="E391" t="s">
-        <v>1436</v>
-      </c>
-      <c r="F391" t="s">
-        <v>1437</v>
-      </c>
-      <c r="G391" t="s">
-        <v>1438</v>
       </c>
       <c r="H391" t="s">
         <v>1187</v>
@@ -17629,7 +17636,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="392" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="392" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A392" s="1">
         <v>390</v>
       </c>
@@ -17640,16 +17647,16 @@
         <v>9</v>
       </c>
       <c r="D392" t="s">
+        <v>1436</v>
+      </c>
+      <c r="E392" t="s">
+        <v>1437</v>
+      </c>
+      <c r="F392" t="s">
+        <v>1438</v>
+      </c>
+      <c r="G392" t="s">
         <v>1439</v>
-      </c>
-      <c r="E392" t="s">
-        <v>1440</v>
-      </c>
-      <c r="F392" t="s">
-        <v>1441</v>
-      </c>
-      <c r="G392" t="s">
-        <v>1442</v>
       </c>
       <c r="H392" t="s">
         <v>166</v>
@@ -17658,7 +17665,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="393" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="393" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A393" s="1">
         <v>391</v>
       </c>
@@ -17669,16 +17676,16 @@
         <v>9</v>
       </c>
       <c r="D393" t="s">
+        <v>1440</v>
+      </c>
+      <c r="E393" t="s">
+        <v>1441</v>
+      </c>
+      <c r="F393" t="s">
+        <v>1442</v>
+      </c>
+      <c r="G393" t="s">
         <v>1443</v>
-      </c>
-      <c r="E393" t="s">
-        <v>1444</v>
-      </c>
-      <c r="F393" t="s">
-        <v>1445</v>
-      </c>
-      <c r="G393" t="s">
-        <v>1446</v>
       </c>
       <c r="H393" t="s">
         <v>1187</v>
@@ -17687,7 +17694,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="394" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="394" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A394" s="1">
         <v>392</v>
       </c>
@@ -17698,16 +17705,16 @@
         <v>9</v>
       </c>
       <c r="D394" t="s">
-        <v>1447</v>
+        <v>1444</v>
       </c>
       <c r="E394" t="s">
-        <v>1448</v>
+        <v>1445</v>
       </c>
       <c r="F394" t="s">
         <v>391</v>
       </c>
       <c r="G394" t="s">
-        <v>1449</v>
+        <v>1446</v>
       </c>
       <c r="H394" t="s">
         <v>1187</v>
@@ -17716,7 +17723,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="395" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="395" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A395" s="1">
         <v>393</v>
       </c>
@@ -17727,16 +17734,16 @@
         <v>9</v>
       </c>
       <c r="D395" t="s">
+        <v>1447</v>
+      </c>
+      <c r="E395" t="s">
+        <v>1448</v>
+      </c>
+      <c r="F395" t="s">
+        <v>1449</v>
+      </c>
+      <c r="G395" t="s">
         <v>1450</v>
-      </c>
-      <c r="E395" t="s">
-        <v>1451</v>
-      </c>
-      <c r="F395" t="s">
-        <v>1452</v>
-      </c>
-      <c r="G395" t="s">
-        <v>1453</v>
       </c>
       <c r="H395" t="s">
         <v>1187</v>
@@ -17745,7 +17752,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="396" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="396" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A396" s="1">
         <v>394</v>
       </c>
@@ -17756,16 +17763,16 @@
         <v>9</v>
       </c>
       <c r="D396" t="s">
-        <v>1454</v>
+        <v>1451</v>
       </c>
       <c r="E396" t="s">
-        <v>1455</v>
+        <v>1452</v>
       </c>
       <c r="F396" t="s">
         <v>391</v>
       </c>
       <c r="G396" t="s">
-        <v>1456</v>
+        <v>1453</v>
       </c>
       <c r="H396" t="s">
         <v>1187</v>
@@ -17774,7 +17781,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="397" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="397" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A397" s="1">
         <v>395</v>
       </c>
@@ -17785,16 +17792,16 @@
         <v>9</v>
       </c>
       <c r="D397" t="s">
+        <v>1454</v>
+      </c>
+      <c r="E397" t="s">
+        <v>1455</v>
+      </c>
+      <c r="F397" t="s">
+        <v>1456</v>
+      </c>
+      <c r="G397" t="s">
         <v>1457</v>
-      </c>
-      <c r="E397" t="s">
-        <v>1458</v>
-      </c>
-      <c r="F397" t="s">
-        <v>1459</v>
-      </c>
-      <c r="G397" t="s">
-        <v>1460</v>
       </c>
       <c r="H397" t="s">
         <v>1187</v>
@@ -17803,7 +17810,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="398" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="398" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A398" s="1">
         <v>396</v>
       </c>
@@ -17814,16 +17821,16 @@
         <v>9</v>
       </c>
       <c r="D398" t="s">
-        <v>1461</v>
+        <v>1458</v>
       </c>
       <c r="E398" t="s">
-        <v>1462</v>
+        <v>1459</v>
       </c>
       <c r="F398" t="s">
         <v>391</v>
       </c>
       <c r="G398" t="s">
-        <v>1463</v>
+        <v>1460</v>
       </c>
       <c r="H398" t="s">
         <v>1187</v>
@@ -17832,7 +17839,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="399" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="399" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A399" s="1">
         <v>397</v>
       </c>
@@ -17843,16 +17850,16 @@
         <v>9</v>
       </c>
       <c r="D399" t="s">
+        <v>1461</v>
+      </c>
+      <c r="E399" t="s">
+        <v>1462</v>
+      </c>
+      <c r="F399" t="s">
+        <v>1463</v>
+      </c>
+      <c r="G399" t="s">
         <v>1464</v>
-      </c>
-      <c r="E399" t="s">
-        <v>1465</v>
-      </c>
-      <c r="F399" t="s">
-        <v>1466</v>
-      </c>
-      <c r="G399" t="s">
-        <v>1467</v>
       </c>
       <c r="H399" t="s">
         <v>1187</v>
@@ -17861,7 +17868,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="400" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="400" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A400" s="1">
         <v>398</v>
       </c>
@@ -17872,16 +17879,16 @@
         <v>9</v>
       </c>
       <c r="D400" t="s">
-        <v>1468</v>
+        <v>1465</v>
       </c>
       <c r="E400" t="s">
-        <v>1469</v>
+        <v>1466</v>
       </c>
       <c r="F400" t="s">
         <v>391</v>
       </c>
       <c r="G400" t="s">
-        <v>1470</v>
+        <v>1467</v>
       </c>
       <c r="H400" t="s">
         <v>1187</v>
@@ -17890,7 +17897,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="401" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="401" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A401" s="1">
         <v>399</v>
       </c>
@@ -17901,16 +17908,16 @@
         <v>9</v>
       </c>
       <c r="D401" t="s">
+        <v>1468</v>
+      </c>
+      <c r="E401" t="s">
+        <v>1469</v>
+      </c>
+      <c r="F401" t="s">
+        <v>1470</v>
+      </c>
+      <c r="G401" t="s">
         <v>1471</v>
-      </c>
-      <c r="E401" t="s">
-        <v>1472</v>
-      </c>
-      <c r="F401" t="s">
-        <v>1473</v>
-      </c>
-      <c r="G401" t="s">
-        <v>1474</v>
       </c>
       <c r="H401" t="s">
         <v>1187</v>
@@ -17919,7 +17926,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="402" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="402" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A402" s="1">
         <v>400</v>
       </c>
@@ -17930,16 +17937,16 @@
         <v>9</v>
       </c>
       <c r="D402" t="s">
-        <v>1475</v>
+        <v>1472</v>
       </c>
       <c r="E402" t="s">
-        <v>1476</v>
+        <v>1473</v>
       </c>
       <c r="F402" t="s">
         <v>391</v>
       </c>
       <c r="G402" t="s">
-        <v>1477</v>
+        <v>1474</v>
       </c>
       <c r="H402" t="s">
         <v>1187</v>
@@ -17948,7 +17955,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="403" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="403" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A403" s="1">
         <v>401</v>
       </c>
@@ -17959,16 +17966,16 @@
         <v>9</v>
       </c>
       <c r="D403" t="s">
+        <v>1475</v>
+      </c>
+      <c r="E403" t="s">
+        <v>1476</v>
+      </c>
+      <c r="F403" t="s">
+        <v>1477</v>
+      </c>
+      <c r="G403" t="s">
         <v>1478</v>
-      </c>
-      <c r="E403" t="s">
-        <v>1479</v>
-      </c>
-      <c r="F403" t="s">
-        <v>1480</v>
-      </c>
-      <c r="G403" t="s">
-        <v>1481</v>
       </c>
       <c r="H403" t="s">
         <v>1187</v>
@@ -17977,7 +17984,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="404" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="404" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A404" s="1">
         <v>402</v>
       </c>
@@ -17988,16 +17995,16 @@
         <v>9</v>
       </c>
       <c r="D404" t="s">
-        <v>1482</v>
+        <v>1479</v>
       </c>
       <c r="E404" t="s">
-        <v>1483</v>
+        <v>1480</v>
       </c>
       <c r="F404" t="s">
         <v>391</v>
       </c>
       <c r="G404" t="s">
-        <v>1484</v>
+        <v>1481</v>
       </c>
       <c r="H404" t="s">
         <v>1187</v>
@@ -18006,7 +18013,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="405" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="405" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A405" s="1">
         <v>403</v>
       </c>
@@ -18017,16 +18024,16 @@
         <v>9</v>
       </c>
       <c r="D405" t="s">
+        <v>1482</v>
+      </c>
+      <c r="E405" t="s">
+        <v>1483</v>
+      </c>
+      <c r="F405" t="s">
+        <v>1484</v>
+      </c>
+      <c r="G405" t="s">
         <v>1485</v>
-      </c>
-      <c r="E405" t="s">
-        <v>1486</v>
-      </c>
-      <c r="F405" t="s">
-        <v>1487</v>
-      </c>
-      <c r="G405" t="s">
-        <v>1488</v>
       </c>
       <c r="H405" t="s">
         <v>1187</v>
@@ -18035,7 +18042,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="406" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="406" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A406" s="1">
         <v>404</v>
       </c>
@@ -18046,16 +18053,16 @@
         <v>9</v>
       </c>
       <c r="D406" t="s">
-        <v>1489</v>
+        <v>1486</v>
       </c>
       <c r="E406" t="s">
-        <v>1490</v>
+        <v>1487</v>
       </c>
       <c r="F406" t="s">
         <v>391</v>
       </c>
       <c r="G406" t="s">
-        <v>1491</v>
+        <v>1488</v>
       </c>
       <c r="H406" t="s">
         <v>1187</v>
@@ -18064,7 +18071,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="407" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="407" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A407" s="1">
         <v>405</v>
       </c>
@@ -18075,16 +18082,16 @@
         <v>9</v>
       </c>
       <c r="D407" t="s">
+        <v>1489</v>
+      </c>
+      <c r="E407" t="s">
+        <v>1490</v>
+      </c>
+      <c r="F407" t="s">
+        <v>1491</v>
+      </c>
+      <c r="G407" t="s">
         <v>1492</v>
-      </c>
-      <c r="E407" t="s">
-        <v>1493</v>
-      </c>
-      <c r="F407" t="s">
-        <v>1494</v>
-      </c>
-      <c r="G407" t="s">
-        <v>1495</v>
       </c>
       <c r="H407" t="s">
         <v>1187</v>
@@ -18093,7 +18100,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="408" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="408" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A408" s="1">
         <v>406</v>
       </c>
@@ -18104,16 +18111,16 @@
         <v>9</v>
       </c>
       <c r="D408" t="s">
-        <v>1496</v>
+        <v>1493</v>
       </c>
       <c r="E408" t="s">
-        <v>1497</v>
+        <v>1494</v>
       </c>
       <c r="F408" t="s">
         <v>391</v>
       </c>
       <c r="G408" t="s">
-        <v>1498</v>
+        <v>1495</v>
       </c>
       <c r="H408" t="s">
         <v>1187</v>
@@ -18122,7 +18129,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="409" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="409" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A409" s="1">
         <v>407</v>
       </c>
@@ -18133,16 +18140,16 @@
         <v>9</v>
       </c>
       <c r="D409" t="s">
+        <v>1496</v>
+      </c>
+      <c r="E409" t="s">
+        <v>1497</v>
+      </c>
+      <c r="F409" t="s">
+        <v>1498</v>
+      </c>
+      <c r="G409" t="s">
         <v>1499</v>
-      </c>
-      <c r="E409" t="s">
-        <v>1500</v>
-      </c>
-      <c r="F409" t="s">
-        <v>1501</v>
-      </c>
-      <c r="G409" t="s">
-        <v>1502</v>
       </c>
       <c r="H409" t="s">
         <v>1187</v>
@@ -18151,7 +18158,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="410" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="410" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A410" s="1">
         <v>408</v>
       </c>
@@ -18162,16 +18169,16 @@
         <v>9</v>
       </c>
       <c r="D410" t="s">
-        <v>1503</v>
+        <v>1500</v>
       </c>
       <c r="E410" t="s">
-        <v>1504</v>
+        <v>1501</v>
       </c>
       <c r="F410" t="s">
         <v>391</v>
       </c>
       <c r="G410" t="s">
-        <v>1505</v>
+        <v>1502</v>
       </c>
       <c r="H410" t="s">
         <v>1187</v>
@@ -18180,7 +18187,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="411" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="411" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A411" s="1">
         <v>409</v>
       </c>
@@ -18191,16 +18198,16 @@
         <v>9</v>
       </c>
       <c r="D411" t="s">
+        <v>1503</v>
+      </c>
+      <c r="E411" t="s">
+        <v>1504</v>
+      </c>
+      <c r="F411" t="s">
+        <v>1505</v>
+      </c>
+      <c r="G411" t="s">
         <v>1506</v>
-      </c>
-      <c r="E411" t="s">
-        <v>1507</v>
-      </c>
-      <c r="F411" t="s">
-        <v>1508</v>
-      </c>
-      <c r="G411" t="s">
-        <v>1509</v>
       </c>
       <c r="H411" t="s">
         <v>1187</v>
@@ -18209,7 +18216,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="412" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="412" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A412" s="1">
         <v>410</v>
       </c>
@@ -18220,16 +18227,16 @@
         <v>9</v>
       </c>
       <c r="D412" t="s">
+        <v>1507</v>
+      </c>
+      <c r="E412" t="s">
+        <v>1508</v>
+      </c>
+      <c r="F412" t="s">
+        <v>1509</v>
+      </c>
+      <c r="G412" t="s">
         <v>1510</v>
-      </c>
-      <c r="E412" t="s">
-        <v>1511</v>
-      </c>
-      <c r="F412" t="s">
-        <v>1512</v>
-      </c>
-      <c r="G412" t="s">
-        <v>1513</v>
       </c>
       <c r="H412" t="s">
         <v>1187</v>
@@ -18238,7 +18245,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="413" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="413" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A413" s="1">
         <v>411</v>
       </c>
@@ -18249,16 +18256,16 @@
         <v>9</v>
       </c>
       <c r="D413" t="s">
-        <v>1514</v>
+        <v>1511</v>
       </c>
       <c r="E413" t="s">
-        <v>1515</v>
+        <v>1512</v>
       </c>
       <c r="F413" t="s">
         <v>391</v>
       </c>
       <c r="G413" t="s">
-        <v>1516</v>
+        <v>1513</v>
       </c>
       <c r="H413" t="s">
         <v>1187</v>
@@ -18267,7 +18274,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="414" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="414" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A414" s="1">
         <v>412</v>
       </c>
@@ -18278,25 +18285,25 @@
         <v>9</v>
       </c>
       <c r="D414" t="s">
-        <v>1517</v>
+        <v>1960</v>
       </c>
       <c r="E414" t="s">
-        <v>1518</v>
+        <v>1514</v>
       </c>
       <c r="F414" t="s">
-        <v>1519</v>
+        <v>1515</v>
       </c>
       <c r="G414" t="s">
-        <v>1520</v>
+        <v>1516</v>
       </c>
       <c r="H414" t="s">
-        <v>1331</v>
+        <v>1329</v>
       </c>
       <c r="I414" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="415" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="415" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A415" s="1">
         <v>413</v>
       </c>
@@ -18307,25 +18314,25 @@
         <v>9</v>
       </c>
       <c r="D415" t="s">
-        <v>1521</v>
+        <v>1517</v>
       </c>
       <c r="E415" t="s">
-        <v>1522</v>
+        <v>1518</v>
       </c>
       <c r="F415" t="s">
         <v>391</v>
       </c>
       <c r="G415" t="s">
-        <v>1523</v>
+        <v>1519</v>
       </c>
       <c r="H415" t="s">
-        <v>1331</v>
+        <v>1329</v>
       </c>
       <c r="I415" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="416" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="416" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A416" s="1">
         <v>414</v>
       </c>
@@ -18336,25 +18343,25 @@
         <v>9</v>
       </c>
       <c r="D416" t="s">
-        <v>1524</v>
+        <v>1959</v>
       </c>
       <c r="E416" t="s">
-        <v>1525</v>
+        <v>1520</v>
       </c>
       <c r="F416" t="s">
-        <v>1526</v>
+        <v>1521</v>
       </c>
       <c r="G416" t="s">
-        <v>1527</v>
+        <v>1522</v>
       </c>
       <c r="H416" t="s">
-        <v>1331</v>
+        <v>1329</v>
       </c>
       <c r="I416" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="417" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="417" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A417" s="1">
         <v>415</v>
       </c>
@@ -18365,25 +18372,25 @@
         <v>9</v>
       </c>
       <c r="D417" t="s">
-        <v>1528</v>
+        <v>1523</v>
       </c>
       <c r="E417" t="s">
-        <v>1529</v>
+        <v>1524</v>
       </c>
       <c r="F417" t="s">
-        <v>1530</v>
+        <v>1525</v>
       </c>
       <c r="G417" t="s">
-        <v>1531</v>
+        <v>1526</v>
       </c>
       <c r="H417" t="s">
-        <v>1331</v>
+        <v>1329</v>
       </c>
       <c r="I417" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="418" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="418" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A418" s="1">
         <v>416</v>
       </c>
@@ -18394,25 +18401,25 @@
         <v>9</v>
       </c>
       <c r="D418" t="s">
-        <v>1532</v>
+        <v>1527</v>
       </c>
       <c r="E418" t="s">
-        <v>1533</v>
+        <v>1528</v>
       </c>
       <c r="F418" t="s">
-        <v>1534</v>
+        <v>1529</v>
       </c>
       <c r="G418" t="s">
-        <v>1535</v>
+        <v>1530</v>
       </c>
       <c r="H418" t="s">
-        <v>1331</v>
+        <v>1329</v>
       </c>
       <c r="I418" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="419" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="419" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A419" s="1">
         <v>417</v>
       </c>
@@ -18423,25 +18430,25 @@
         <v>9</v>
       </c>
       <c r="D419" t="s">
-        <v>1536</v>
+        <v>1531</v>
       </c>
       <c r="E419" t="s">
-        <v>1537</v>
+        <v>1532</v>
       </c>
       <c r="F419" t="s">
-        <v>1538</v>
+        <v>1533</v>
       </c>
       <c r="G419" t="s">
-        <v>1539</v>
+        <v>1534</v>
       </c>
       <c r="H419" t="s">
-        <v>1331</v>
+        <v>1329</v>
       </c>
       <c r="I419" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="420" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="420" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A420" s="1">
         <v>418</v>
       </c>
@@ -18452,25 +18459,25 @@
         <v>9</v>
       </c>
       <c r="D420" t="s">
-        <v>1540</v>
+        <v>1535</v>
       </c>
       <c r="E420" t="s">
-        <v>1541</v>
+        <v>1536</v>
       </c>
       <c r="F420" t="s">
-        <v>1542</v>
+        <v>1537</v>
       </c>
       <c r="G420" t="s">
-        <v>1543</v>
+        <v>1538</v>
       </c>
       <c r="H420" t="s">
-        <v>1331</v>
+        <v>1329</v>
       </c>
       <c r="I420" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="421" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="421" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A421" s="1">
         <v>419</v>
       </c>
@@ -18481,25 +18488,25 @@
         <v>9</v>
       </c>
       <c r="D421" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="E421" t="s">
-        <v>1545</v>
+        <v>1540</v>
       </c>
       <c r="F421" t="s">
-        <v>1546</v>
+        <v>1541</v>
       </c>
       <c r="G421" t="s">
-        <v>1547</v>
+        <v>1542</v>
       </c>
       <c r="H421" t="s">
-        <v>1331</v>
+        <v>1329</v>
       </c>
       <c r="I421" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="422" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="422" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A422" s="1">
         <v>420</v>
       </c>
@@ -18510,25 +18517,25 @@
         <v>9</v>
       </c>
       <c r="D422" t="s">
-        <v>1548</v>
+        <v>1543</v>
       </c>
       <c r="E422" t="s">
-        <v>1549</v>
+        <v>1544</v>
       </c>
       <c r="F422" t="s">
-        <v>1550</v>
+        <v>1545</v>
       </c>
       <c r="G422" t="s">
-        <v>1551</v>
+        <v>1546</v>
       </c>
       <c r="H422" t="s">
-        <v>1331</v>
+        <v>1329</v>
       </c>
       <c r="I422" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="423" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="423" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A423" s="1">
         <v>421</v>
       </c>
@@ -18539,25 +18546,25 @@
         <v>9</v>
       </c>
       <c r="D423" t="s">
-        <v>1552</v>
+        <v>1547</v>
       </c>
       <c r="E423" t="s">
-        <v>1553</v>
+        <v>1548</v>
       </c>
       <c r="F423" t="s">
-        <v>1554</v>
+        <v>1549</v>
       </c>
       <c r="G423" t="s">
-        <v>1555</v>
+        <v>1550</v>
       </c>
       <c r="H423" t="s">
-        <v>1331</v>
+        <v>1329</v>
       </c>
       <c r="I423" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="424" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="424" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A424" s="1">
         <v>422</v>
       </c>
@@ -18568,25 +18575,25 @@
         <v>9</v>
       </c>
       <c r="D424" t="s">
-        <v>1556</v>
+        <v>1551</v>
       </c>
       <c r="E424" t="s">
-        <v>1557</v>
+        <v>1552</v>
       </c>
       <c r="F424" t="s">
-        <v>1558</v>
+        <v>1553</v>
       </c>
       <c r="G424" t="s">
-        <v>1559</v>
+        <v>1554</v>
       </c>
       <c r="H424" t="s">
-        <v>1331</v>
+        <v>1329</v>
       </c>
       <c r="I424" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="425" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="425" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A425" s="1">
         <v>423</v>
       </c>
@@ -18597,25 +18604,25 @@
         <v>9</v>
       </c>
       <c r="D425" t="s">
-        <v>1560</v>
+        <v>1555</v>
       </c>
       <c r="E425" t="s">
-        <v>1561</v>
+        <v>1556</v>
       </c>
       <c r="F425" t="s">
-        <v>1562</v>
+        <v>1557</v>
       </c>
       <c r="G425" t="s">
-        <v>1563</v>
+        <v>1558</v>
       </c>
       <c r="H425" t="s">
-        <v>1331</v>
+        <v>1329</v>
       </c>
       <c r="I425" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="426" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="426" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A426" s="1">
         <v>424</v>
       </c>
@@ -18626,25 +18633,25 @@
         <v>9</v>
       </c>
       <c r="D426" t="s">
-        <v>1564</v>
+        <v>1559</v>
       </c>
       <c r="E426" t="s">
-        <v>1565</v>
+        <v>1560</v>
       </c>
       <c r="F426" t="s">
-        <v>1566</v>
+        <v>1561</v>
       </c>
       <c r="G426" t="s">
-        <v>1567</v>
+        <v>1562</v>
       </c>
       <c r="H426" t="s">
-        <v>1331</v>
+        <v>1329</v>
       </c>
       <c r="I426" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="427" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="427" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A427" s="1">
         <v>425</v>
       </c>
@@ -18655,25 +18662,25 @@
         <v>9</v>
       </c>
       <c r="D427" t="s">
-        <v>1568</v>
+        <v>1563</v>
       </c>
       <c r="E427" t="s">
-        <v>1569</v>
+        <v>1564</v>
       </c>
       <c r="F427" t="s">
-        <v>1570</v>
+        <v>1565</v>
       </c>
       <c r="G427" t="s">
-        <v>1571</v>
+        <v>1566</v>
       </c>
       <c r="H427" t="s">
-        <v>1331</v>
+        <v>1329</v>
       </c>
       <c r="I427" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="428" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="428" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A428" s="1">
         <v>426</v>
       </c>
@@ -18684,25 +18691,25 @@
         <v>9</v>
       </c>
       <c r="D428" t="s">
-        <v>1572</v>
+        <v>1567</v>
       </c>
       <c r="E428" t="s">
-        <v>1573</v>
+        <v>1568</v>
       </c>
       <c r="F428" t="s">
-        <v>1574</v>
+        <v>1569</v>
       </c>
       <c r="G428" t="s">
-        <v>1575</v>
+        <v>1570</v>
       </c>
       <c r="H428" t="s">
-        <v>1331</v>
+        <v>1329</v>
       </c>
       <c r="I428" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="429" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="429" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A429" s="1">
         <v>427</v>
       </c>
@@ -18713,25 +18720,25 @@
         <v>9</v>
       </c>
       <c r="D429" t="s">
-        <v>1576</v>
+        <v>1571</v>
       </c>
       <c r="E429" t="s">
-        <v>1577</v>
+        <v>1572</v>
       </c>
       <c r="F429" t="s">
-        <v>1578</v>
+        <v>1573</v>
       </c>
       <c r="G429" t="s">
-        <v>1579</v>
+        <v>1574</v>
       </c>
       <c r="H429" t="s">
-        <v>1331</v>
+        <v>1329</v>
       </c>
       <c r="I429" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="430" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="430" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A430" s="1">
         <v>428</v>
       </c>
@@ -18742,25 +18749,25 @@
         <v>9</v>
       </c>
       <c r="D430" t="s">
-        <v>1580</v>
+        <v>1575</v>
       </c>
       <c r="E430" t="s">
-        <v>1581</v>
+        <v>1576</v>
       </c>
       <c r="F430" t="s">
-        <v>1582</v>
+        <v>1577</v>
       </c>
       <c r="G430" t="s">
-        <v>1583</v>
+        <v>1578</v>
       </c>
       <c r="H430" t="s">
-        <v>1331</v>
+        <v>1329</v>
       </c>
       <c r="I430" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="431" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="431" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A431" s="1">
         <v>429</v>
       </c>
@@ -18771,25 +18778,25 @@
         <v>9</v>
       </c>
       <c r="D431" t="s">
-        <v>1584</v>
+        <v>1579</v>
       </c>
       <c r="E431" t="s">
-        <v>1585</v>
+        <v>1580</v>
       </c>
       <c r="F431" t="s">
-        <v>1586</v>
+        <v>1581</v>
       </c>
       <c r="G431" t="s">
-        <v>1587</v>
+        <v>1582</v>
       </c>
       <c r="H431" t="s">
-        <v>1331</v>
+        <v>1329</v>
       </c>
       <c r="I431" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="432" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="432" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A432" s="1">
         <v>430</v>
       </c>
@@ -18800,25 +18807,25 @@
         <v>9</v>
       </c>
       <c r="D432" t="s">
-        <v>1588</v>
+        <v>1583</v>
       </c>
       <c r="E432" t="s">
-        <v>1589</v>
+        <v>1584</v>
       </c>
       <c r="F432" t="s">
-        <v>1590</v>
+        <v>1585</v>
       </c>
       <c r="G432" t="s">
-        <v>1591</v>
+        <v>1586</v>
       </c>
       <c r="H432" t="s">
-        <v>1331</v>
+        <v>1329</v>
       </c>
       <c r="I432" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="433" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="433" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A433" s="1">
         <v>431</v>
       </c>
@@ -18829,25 +18836,25 @@
         <v>9</v>
       </c>
       <c r="D433" t="s">
-        <v>1592</v>
+        <v>1587</v>
       </c>
       <c r="E433" t="s">
-        <v>1593</v>
+        <v>1588</v>
       </c>
       <c r="F433" t="s">
-        <v>1594</v>
+        <v>1589</v>
       </c>
       <c r="G433" t="s">
-        <v>1595</v>
+        <v>1590</v>
       </c>
       <c r="H433" t="s">
-        <v>1331</v>
+        <v>1329</v>
       </c>
       <c r="I433" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="434" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="434" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A434" s="1">
         <v>432</v>
       </c>
@@ -18858,25 +18865,25 @@
         <v>9</v>
       </c>
       <c r="D434" t="s">
-        <v>1596</v>
+        <v>1591</v>
       </c>
       <c r="E434" t="s">
-        <v>1597</v>
+        <v>1592</v>
       </c>
       <c r="F434" t="s">
-        <v>1598</v>
+        <v>1593</v>
       </c>
       <c r="G434" t="s">
-        <v>1599</v>
+        <v>1594</v>
       </c>
       <c r="H434" t="s">
-        <v>1331</v>
+        <v>1329</v>
       </c>
       <c r="I434" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="435" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="435" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A435" s="1">
         <v>433</v>
       </c>
@@ -18887,25 +18894,25 @@
         <v>9</v>
       </c>
       <c r="D435" t="s">
-        <v>1600</v>
+        <v>1595</v>
       </c>
       <c r="E435" t="s">
-        <v>1601</v>
+        <v>1596</v>
       </c>
       <c r="F435" t="s">
-        <v>1602</v>
+        <v>1597</v>
       </c>
       <c r="G435" t="s">
-        <v>1603</v>
+        <v>1598</v>
       </c>
       <c r="H435" t="s">
-        <v>1331</v>
+        <v>1329</v>
       </c>
       <c r="I435" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="436" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="436" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A436" s="1">
         <v>434</v>
       </c>
@@ -18916,25 +18923,25 @@
         <v>9</v>
       </c>
       <c r="D436" t="s">
-        <v>1604</v>
+        <v>1599</v>
       </c>
       <c r="E436" t="s">
-        <v>1605</v>
+        <v>1600</v>
       </c>
       <c r="F436" t="s">
-        <v>1606</v>
+        <v>1601</v>
       </c>
       <c r="G436" t="s">
-        <v>1607</v>
+        <v>1602</v>
       </c>
       <c r="H436" t="s">
-        <v>1331</v>
+        <v>1329</v>
       </c>
       <c r="I436" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="437" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="437" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A437" s="1">
         <v>435</v>
       </c>
@@ -18945,25 +18952,25 @@
         <v>9</v>
       </c>
       <c r="D437" t="s">
-        <v>1608</v>
+        <v>1603</v>
       </c>
       <c r="E437" t="s">
-        <v>1609</v>
+        <v>1604</v>
       </c>
       <c r="F437" t="s">
-        <v>1610</v>
+        <v>1605</v>
       </c>
       <c r="G437" t="s">
-        <v>1611</v>
+        <v>1606</v>
       </c>
       <c r="H437" t="s">
-        <v>1331</v>
+        <v>1329</v>
       </c>
       <c r="I437" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="438" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="438" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A438" s="1">
         <v>436</v>
       </c>
@@ -18974,25 +18981,25 @@
         <v>9</v>
       </c>
       <c r="D438" t="s">
-        <v>1612</v>
+        <v>1607</v>
       </c>
       <c r="E438" t="s">
-        <v>1613</v>
+        <v>1608</v>
       </c>
       <c r="F438" t="s">
-        <v>1614</v>
+        <v>1609</v>
       </c>
       <c r="G438" t="s">
-        <v>1615</v>
+        <v>1610</v>
       </c>
       <c r="H438" t="s">
-        <v>1616</v>
+        <v>1611</v>
       </c>
       <c r="I438" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="439" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="439" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A439" s="1">
         <v>437</v>
       </c>
@@ -19003,25 +19010,25 @@
         <v>9</v>
       </c>
       <c r="D439" t="s">
-        <v>1617</v>
+        <v>1612</v>
       </c>
       <c r="E439" t="s">
-        <v>1618</v>
+        <v>1613</v>
       </c>
       <c r="F439" t="s">
-        <v>1619</v>
+        <v>1614</v>
       </c>
       <c r="G439" t="s">
-        <v>1620</v>
+        <v>1615</v>
       </c>
       <c r="H439" t="s">
-        <v>1299</v>
+        <v>1297</v>
       </c>
       <c r="I439" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="440" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="440" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A440" s="1">
         <v>438</v>
       </c>
@@ -19032,25 +19039,25 @@
         <v>9</v>
       </c>
       <c r="D440" t="s">
-        <v>1621</v>
+        <v>1616</v>
       </c>
       <c r="E440" t="s">
-        <v>1622</v>
+        <v>1617</v>
       </c>
       <c r="F440" t="s">
-        <v>1623</v>
+        <v>1618</v>
       </c>
       <c r="G440" t="s">
-        <v>1624</v>
+        <v>1619</v>
       </c>
       <c r="H440" t="s">
-        <v>1331</v>
+        <v>1329</v>
       </c>
       <c r="I440" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="441" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="441" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A441" s="1">
         <v>439</v>
       </c>
@@ -19061,25 +19068,25 @@
         <v>9</v>
       </c>
       <c r="D441" t="s">
-        <v>1625</v>
+        <v>1620</v>
       </c>
       <c r="E441" t="s">
-        <v>1626</v>
+        <v>1621</v>
       </c>
       <c r="F441" t="s">
-        <v>1627</v>
+        <v>1622</v>
       </c>
       <c r="G441" t="s">
-        <v>1628</v>
+        <v>1623</v>
       </c>
       <c r="H441" t="s">
-        <v>1629</v>
+        <v>1624</v>
       </c>
       <c r="I441" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="442" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="442" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A442" s="1">
         <v>440</v>
       </c>
@@ -19090,25 +19097,25 @@
         <v>9</v>
       </c>
       <c r="D442" t="s">
-        <v>1630</v>
+        <v>1625</v>
       </c>
       <c r="E442" t="s">
-        <v>1631</v>
+        <v>1626</v>
       </c>
       <c r="F442" t="s">
-        <v>1632</v>
+        <v>1627</v>
       </c>
       <c r="G442" t="s">
-        <v>1633</v>
+        <v>1628</v>
       </c>
       <c r="H442" t="s">
-        <v>1331</v>
+        <v>1329</v>
       </c>
       <c r="I442" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="443" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="443" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A443" s="1">
         <v>441</v>
       </c>
@@ -19119,25 +19126,25 @@
         <v>9</v>
       </c>
       <c r="D443" t="s">
-        <v>1634</v>
+        <v>1629</v>
       </c>
       <c r="E443" t="s">
-        <v>1635</v>
+        <v>1630</v>
       </c>
       <c r="F443" t="s">
-        <v>1636</v>
+        <v>1631</v>
       </c>
       <c r="G443" t="s">
-        <v>1637</v>
+        <v>1632</v>
       </c>
       <c r="H443" t="s">
-        <v>1326</v>
+        <v>1324</v>
       </c>
       <c r="I443" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="444" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="444" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A444" s="1">
         <v>442</v>
       </c>
@@ -19148,25 +19155,25 @@
         <v>9</v>
       </c>
       <c r="D444" t="s">
-        <v>1638</v>
+        <v>1633</v>
       </c>
       <c r="E444" t="s">
-        <v>1639</v>
+        <v>1634</v>
       </c>
       <c r="F444" t="s">
-        <v>1640</v>
+        <v>1635</v>
       </c>
       <c r="G444" t="s">
-        <v>1641</v>
+        <v>1636</v>
       </c>
       <c r="H444" t="s">
-        <v>1336</v>
+        <v>1334</v>
       </c>
       <c r="I444" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="445" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="445" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A445" s="1">
         <v>443</v>
       </c>
@@ -19177,25 +19184,25 @@
         <v>9</v>
       </c>
       <c r="D445" t="s">
-        <v>1642</v>
+        <v>1637</v>
       </c>
       <c r="E445" t="s">
-        <v>1643</v>
+        <v>1638</v>
       </c>
       <c r="F445" t="s">
-        <v>1644</v>
+        <v>1639</v>
       </c>
       <c r="G445" t="s">
-        <v>1645</v>
+        <v>1640</v>
       </c>
       <c r="H445" t="s">
-        <v>1341</v>
+        <v>1339</v>
       </c>
       <c r="I445" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="446" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="446" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A446" s="1">
         <v>444</v>
       </c>
@@ -19206,25 +19213,25 @@
         <v>9</v>
       </c>
       <c r="D446" t="s">
-        <v>1646</v>
+        <v>1641</v>
       </c>
       <c r="E446" t="s">
-        <v>1647</v>
+        <v>1642</v>
       </c>
       <c r="F446" t="s">
-        <v>1648</v>
+        <v>1643</v>
       </c>
       <c r="G446" t="s">
-        <v>1649</v>
+        <v>1644</v>
       </c>
       <c r="H446" t="s">
-        <v>1346</v>
+        <v>1344</v>
       </c>
       <c r="I446" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="447" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="447" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A447" s="1">
         <v>445</v>
       </c>
@@ -19235,25 +19242,25 @@
         <v>9</v>
       </c>
       <c r="D447" t="s">
-        <v>1650</v>
+        <v>1645</v>
       </c>
       <c r="E447" t="s">
-        <v>1651</v>
+        <v>1646</v>
       </c>
       <c r="F447" t="s">
-        <v>1652</v>
+        <v>1647</v>
       </c>
       <c r="G447" t="s">
-        <v>1653</v>
+        <v>1648</v>
       </c>
       <c r="H447" t="s">
-        <v>1331</v>
+        <v>1329</v>
       </c>
       <c r="I447" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="448" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="448" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A448" s="1">
         <v>446</v>
       </c>
@@ -19264,25 +19271,25 @@
         <v>9</v>
       </c>
       <c r="D448" t="s">
-        <v>1654</v>
+        <v>1649</v>
       </c>
       <c r="E448" t="s">
-        <v>1655</v>
+        <v>1650</v>
       </c>
       <c r="F448" t="s">
-        <v>1656</v>
+        <v>1651</v>
       </c>
       <c r="G448" t="s">
-        <v>1657</v>
+        <v>1652</v>
       </c>
       <c r="H448" t="s">
-        <v>1331</v>
+        <v>1329</v>
       </c>
       <c r="I448" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="449" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="449" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A449" s="1">
         <v>447</v>
       </c>
@@ -19293,25 +19300,25 @@
         <v>9</v>
       </c>
       <c r="D449" t="s">
-        <v>1658</v>
+        <v>1653</v>
       </c>
       <c r="E449" t="s">
-        <v>1659</v>
+        <v>1654</v>
       </c>
       <c r="F449" t="s">
-        <v>1660</v>
+        <v>1655</v>
       </c>
       <c r="G449" t="s">
-        <v>1661</v>
+        <v>1656</v>
       </c>
       <c r="H449" t="s">
-        <v>1364</v>
+        <v>1362</v>
       </c>
       <c r="I449" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="450" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="450" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A450" s="1">
         <v>448</v>
       </c>
@@ -19322,25 +19329,25 @@
         <v>9</v>
       </c>
       <c r="D450" t="s">
-        <v>1662</v>
+        <v>1657</v>
       </c>
       <c r="E450" t="s">
-        <v>1663</v>
+        <v>1658</v>
       </c>
       <c r="F450" t="s">
-        <v>1664</v>
+        <v>1659</v>
       </c>
       <c r="G450" t="s">
-        <v>1665</v>
+        <v>1660</v>
       </c>
       <c r="H450" t="s">
-        <v>1364</v>
+        <v>1362</v>
       </c>
       <c r="I450" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="451" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="451" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A451" s="1">
         <v>449</v>
       </c>
@@ -19351,25 +19358,25 @@
         <v>9</v>
       </c>
       <c r="D451" t="s">
-        <v>1666</v>
+        <v>1661</v>
       </c>
       <c r="E451" t="s">
-        <v>1667</v>
+        <v>1662</v>
       </c>
       <c r="F451" t="s">
-        <v>1668</v>
+        <v>1663</v>
       </c>
       <c r="G451" t="s">
-        <v>1669</v>
+        <v>1664</v>
       </c>
       <c r="H451" t="s">
-        <v>1369</v>
+        <v>1367</v>
       </c>
       <c r="I451" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="452" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="452" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A452" s="1">
         <v>450</v>
       </c>
@@ -19380,25 +19387,25 @@
         <v>9</v>
       </c>
       <c r="D452" t="s">
-        <v>1670</v>
+        <v>1665</v>
       </c>
       <c r="E452" t="s">
-        <v>1671</v>
+        <v>1666</v>
       </c>
       <c r="F452" t="s">
-        <v>1672</v>
+        <v>1667</v>
       </c>
       <c r="G452" t="s">
-        <v>1673</v>
+        <v>1668</v>
       </c>
       <c r="H452" t="s">
-        <v>1369</v>
+        <v>1367</v>
       </c>
       <c r="I452" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="453" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="453" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A453" s="1">
         <v>451</v>
       </c>
@@ -19409,25 +19416,25 @@
         <v>9</v>
       </c>
       <c r="D453" t="s">
-        <v>1674</v>
+        <v>1669</v>
       </c>
       <c r="E453" t="s">
-        <v>1675</v>
+        <v>1670</v>
       </c>
       <c r="F453" t="s">
-        <v>1676</v>
+        <v>1671</v>
       </c>
       <c r="G453" t="s">
-        <v>1677</v>
+        <v>1672</v>
       </c>
       <c r="H453" t="s">
-        <v>1369</v>
+        <v>1367</v>
       </c>
       <c r="I453" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="454" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="454" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A454" s="1">
         <v>452</v>
       </c>
@@ -19438,25 +19445,25 @@
         <v>9</v>
       </c>
       <c r="D454" t="s">
-        <v>1678</v>
+        <v>1673</v>
       </c>
       <c r="E454" t="s">
-        <v>1679</v>
+        <v>1674</v>
       </c>
       <c r="F454" t="s">
-        <v>1680</v>
+        <v>1675</v>
       </c>
       <c r="G454" t="s">
-        <v>1681</v>
+        <v>1676</v>
       </c>
       <c r="H454" t="s">
-        <v>1369</v>
+        <v>1367</v>
       </c>
       <c r="I454" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="455" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="455" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A455" s="1">
         <v>453</v>
       </c>
@@ -19467,25 +19474,25 @@
         <v>9</v>
       </c>
       <c r="D455" t="s">
-        <v>1682</v>
+        <v>1677</v>
       </c>
       <c r="E455" t="s">
-        <v>1683</v>
+        <v>1678</v>
       </c>
       <c r="F455" t="s">
-        <v>1684</v>
+        <v>1679</v>
       </c>
       <c r="G455" t="s">
-        <v>1685</v>
+        <v>1680</v>
       </c>
       <c r="H455" t="s">
-        <v>1369</v>
+        <v>1367</v>
       </c>
       <c r="I455" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="456" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="456" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A456" s="1">
         <v>454</v>
       </c>
@@ -19496,25 +19503,25 @@
         <v>9</v>
       </c>
       <c r="D456" t="s">
-        <v>1686</v>
+        <v>1681</v>
       </c>
       <c r="E456" t="s">
-        <v>1687</v>
+        <v>1682</v>
       </c>
       <c r="F456" t="s">
-        <v>1688</v>
+        <v>1683</v>
       </c>
       <c r="G456" t="s">
-        <v>1689</v>
+        <v>1684</v>
       </c>
       <c r="H456" t="s">
-        <v>1369</v>
+        <v>1367</v>
       </c>
       <c r="I456" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="457" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="457" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A457" s="1">
         <v>455</v>
       </c>
@@ -19525,25 +19532,25 @@
         <v>9</v>
       </c>
       <c r="D457" t="s">
-        <v>1690</v>
+        <v>1685</v>
       </c>
       <c r="E457" t="s">
-        <v>1691</v>
+        <v>1686</v>
       </c>
       <c r="F457" t="s">
-        <v>1692</v>
+        <v>1687</v>
       </c>
       <c r="G457" t="s">
-        <v>1693</v>
+        <v>1688</v>
       </c>
       <c r="H457" t="s">
-        <v>1369</v>
+        <v>1367</v>
       </c>
       <c r="I457" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="458" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="458" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A458" s="1">
         <v>456</v>
       </c>
@@ -19554,25 +19561,25 @@
         <v>9</v>
       </c>
       <c r="D458" t="s">
-        <v>1694</v>
+        <v>1689</v>
       </c>
       <c r="E458" t="s">
-        <v>1695</v>
+        <v>1690</v>
       </c>
       <c r="F458" t="s">
-        <v>1696</v>
+        <v>1691</v>
       </c>
       <c r="G458" t="s">
-        <v>1697</v>
+        <v>1692</v>
       </c>
       <c r="H458" t="s">
-        <v>1369</v>
+        <v>1367</v>
       </c>
       <c r="I458" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="459" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="459" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A459" s="1">
         <v>457</v>
       </c>
@@ -19583,25 +19590,25 @@
         <v>9</v>
       </c>
       <c r="D459" t="s">
-        <v>1698</v>
+        <v>1693</v>
       </c>
       <c r="E459" t="s">
-        <v>1699</v>
+        <v>1694</v>
       </c>
       <c r="F459" t="s">
-        <v>1700</v>
+        <v>1695</v>
       </c>
       <c r="G459" t="s">
-        <v>1701</v>
+        <v>1696</v>
       </c>
       <c r="H459" t="s">
-        <v>1369</v>
+        <v>1367</v>
       </c>
       <c r="I459" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="460" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="460" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A460" s="1">
         <v>458</v>
       </c>
@@ -19612,25 +19619,25 @@
         <v>9</v>
       </c>
       <c r="D460" t="s">
-        <v>1702</v>
+        <v>1697</v>
       </c>
       <c r="E460" t="s">
-        <v>1703</v>
+        <v>1698</v>
       </c>
       <c r="F460" t="s">
-        <v>1704</v>
+        <v>1699</v>
       </c>
       <c r="G460" t="s">
-        <v>1705</v>
+        <v>1700</v>
       </c>
       <c r="H460" t="s">
-        <v>1369</v>
+        <v>1367</v>
       </c>
       <c r="I460" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="461" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="461" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A461" s="1">
         <v>459</v>
       </c>
@@ -19641,25 +19648,25 @@
         <v>9</v>
       </c>
       <c r="D461" t="s">
-        <v>1706</v>
+        <v>1701</v>
       </c>
       <c r="E461" t="s">
-        <v>1707</v>
+        <v>1702</v>
       </c>
       <c r="F461" t="s">
-        <v>1708</v>
+        <v>1703</v>
       </c>
       <c r="G461" t="s">
-        <v>1709</v>
+        <v>1704</v>
       </c>
       <c r="H461" t="s">
-        <v>1710</v>
+        <v>1705</v>
       </c>
       <c r="I461" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="462" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="462" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A462" s="1">
         <v>460</v>
       </c>
@@ -19670,25 +19677,25 @@
         <v>9</v>
       </c>
       <c r="D462" t="s">
-        <v>1711</v>
+        <v>1706</v>
       </c>
       <c r="E462" t="s">
-        <v>1712</v>
+        <v>1707</v>
       </c>
       <c r="F462" t="s">
-        <v>1713</v>
+        <v>1708</v>
       </c>
       <c r="G462" t="s">
-        <v>1714</v>
+        <v>1709</v>
       </c>
       <c r="H462" t="s">
-        <v>1715</v>
+        <v>1710</v>
       </c>
       <c r="I462" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="463" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="463" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A463" s="1">
         <v>461</v>
       </c>
@@ -19699,16 +19706,16 @@
         <v>9</v>
       </c>
       <c r="D463" t="s">
-        <v>1716</v>
+        <v>1711</v>
       </c>
       <c r="E463" t="s">
-        <v>1717</v>
+        <v>1712</v>
       </c>
       <c r="F463" t="s">
-        <v>1718</v>
+        <v>1713</v>
       </c>
       <c r="G463" t="s">
-        <v>1719</v>
+        <v>1714</v>
       </c>
       <c r="H463" t="s">
         <v>1114</v>
@@ -19717,7 +19724,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="464" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="464" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A464" s="1">
         <v>462</v>
       </c>
@@ -19728,16 +19735,16 @@
         <v>9</v>
       </c>
       <c r="D464" t="s">
-        <v>1720</v>
+        <v>1715</v>
       </c>
       <c r="E464" t="s">
-        <v>1721</v>
+        <v>1716</v>
       </c>
       <c r="F464" t="s">
         <v>1112</v>
       </c>
       <c r="G464" t="s">
-        <v>1722</v>
+        <v>1717</v>
       </c>
       <c r="H464" t="s">
         <v>1114</v>
@@ -19746,7 +19753,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="465" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="465" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A465" s="1">
         <v>463</v>
       </c>
@@ -19757,16 +19764,16 @@
         <v>9</v>
       </c>
       <c r="D465" t="s">
-        <v>1723</v>
+        <v>1718</v>
       </c>
       <c r="E465" t="s">
-        <v>1724</v>
+        <v>1719</v>
       </c>
       <c r="F465" t="s">
         <v>1117</v>
       </c>
       <c r="G465" t="s">
-        <v>1725</v>
+        <v>1720</v>
       </c>
       <c r="H465" t="s">
         <v>1114</v>
@@ -19775,7 +19782,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="466" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="466" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A466" s="1">
         <v>464</v>
       </c>
@@ -19786,16 +19793,16 @@
         <v>9</v>
       </c>
       <c r="D466" t="s">
-        <v>1726</v>
+        <v>1721</v>
       </c>
       <c r="E466" t="s">
-        <v>1727</v>
+        <v>1722</v>
       </c>
       <c r="F466" t="s">
-        <v>1728</v>
+        <v>1723</v>
       </c>
       <c r="G466" t="s">
-        <v>1729</v>
+        <v>1724</v>
       </c>
       <c r="H466" t="s">
         <v>1158</v>
@@ -19804,7 +19811,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="467" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="467" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A467" s="1">
         <v>465</v>
       </c>
@@ -19815,16 +19822,16 @@
         <v>9</v>
       </c>
       <c r="D467" t="s">
-        <v>1730</v>
+        <v>1725</v>
       </c>
       <c r="E467" t="s">
-        <v>1731</v>
+        <v>1726</v>
       </c>
       <c r="F467" t="s">
-        <v>1732</v>
+        <v>1727</v>
       </c>
       <c r="G467" t="s">
-        <v>1733</v>
+        <v>1728</v>
       </c>
       <c r="H467" t="s">
         <v>1167</v>
@@ -19833,7 +19840,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="468" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="468" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A468" s="1">
         <v>466</v>
       </c>
@@ -19844,25 +19851,25 @@
         <v>9</v>
       </c>
       <c r="D468" t="s">
-        <v>1734</v>
+        <v>1729</v>
       </c>
       <c r="E468" t="s">
-        <v>1735</v>
+        <v>1730</v>
       </c>
       <c r="F468" t="s">
-        <v>1736</v>
+        <v>1731</v>
       </c>
       <c r="G468" t="s">
-        <v>1737</v>
+        <v>1732</v>
       </c>
       <c r="H468" t="s">
-        <v>1419</v>
+        <v>1417</v>
       </c>
       <c r="I468" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="469" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="469" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A469" s="1">
         <v>467</v>
       </c>
@@ -19873,22 +19880,22 @@
         <v>9</v>
       </c>
       <c r="D469" t="s">
-        <v>1738</v>
+        <v>1962</v>
       </c>
       <c r="E469" t="s">
-        <v>1739</v>
+        <v>1733</v>
       </c>
       <c r="F469" t="s">
-        <v>1740</v>
+        <v>1734</v>
       </c>
       <c r="G469" t="s">
-        <v>1741</v>
+        <v>1735</v>
       </c>
       <c r="H469" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="470" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="470" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A470" s="1">
         <v>468</v>
       </c>
@@ -19899,22 +19906,22 @@
         <v>9</v>
       </c>
       <c r="D470" t="s">
-        <v>1742</v>
+        <v>1736</v>
       </c>
       <c r="E470" t="s">
-        <v>1743</v>
+        <v>1737</v>
       </c>
       <c r="F470" t="s">
-        <v>1744</v>
+        <v>1738</v>
       </c>
       <c r="G470" t="s">
-        <v>1745</v>
+        <v>1739</v>
       </c>
       <c r="H470" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="471" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="471" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A471" s="1">
         <v>469</v>
       </c>
@@ -19925,25 +19932,25 @@
         <v>9</v>
       </c>
       <c r="D471" t="s">
-        <v>1746</v>
+        <v>1740</v>
       </c>
       <c r="E471" t="s">
-        <v>1747</v>
+        <v>1741</v>
       </c>
       <c r="F471" t="s">
-        <v>1748</v>
+        <v>1742</v>
       </c>
       <c r="G471" t="s">
-        <v>1749</v>
+        <v>1743</v>
       </c>
       <c r="H471" t="s">
-        <v>1750</v>
+        <v>1744</v>
       </c>
       <c r="I471" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="472" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="472" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A472" s="1">
         <v>470</v>
       </c>
@@ -19954,25 +19961,25 @@
         <v>9</v>
       </c>
       <c r="D472" t="s">
-        <v>1751</v>
+        <v>1745</v>
       </c>
       <c r="E472" t="s">
-        <v>1752</v>
+        <v>1746</v>
       </c>
       <c r="F472" t="s">
-        <v>1753</v>
+        <v>1747</v>
       </c>
       <c r="G472" t="s">
-        <v>1754</v>
+        <v>1748</v>
       </c>
       <c r="H472" t="s">
-        <v>1755</v>
+        <v>1749</v>
       </c>
       <c r="I472" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="473" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="473" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A473" s="1">
         <v>471</v>
       </c>
@@ -19983,25 +19990,25 @@
         <v>9</v>
       </c>
       <c r="D473" t="s">
-        <v>1756</v>
+        <v>1750</v>
       </c>
       <c r="E473" t="s">
-        <v>1757</v>
+        <v>1751</v>
       </c>
       <c r="F473" t="s">
-        <v>1758</v>
+        <v>1752</v>
       </c>
       <c r="G473" t="s">
-        <v>1759</v>
+        <v>1753</v>
       </c>
       <c r="H473" t="s">
-        <v>1760</v>
+        <v>1754</v>
       </c>
       <c r="I473" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="474" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="474" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A474" s="1">
         <v>472</v>
       </c>
@@ -20012,25 +20019,25 @@
         <v>9</v>
       </c>
       <c r="D474" t="s">
-        <v>1761</v>
+        <v>1755</v>
       </c>
       <c r="E474" t="s">
-        <v>1762</v>
+        <v>1756</v>
       </c>
       <c r="F474" t="s">
-        <v>1763</v>
+        <v>1757</v>
       </c>
       <c r="G474" t="s">
-        <v>1764</v>
+        <v>1758</v>
       </c>
       <c r="H474" t="s">
-        <v>1760</v>
+        <v>1754</v>
       </c>
       <c r="I474" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="475" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="475" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A475" s="1">
         <v>473</v>
       </c>
@@ -20041,25 +20048,25 @@
         <v>9</v>
       </c>
       <c r="D475" t="s">
-        <v>1765</v>
+        <v>1759</v>
       </c>
       <c r="E475" t="s">
-        <v>1766</v>
+        <v>1760</v>
       </c>
       <c r="F475" t="s">
-        <v>1767</v>
+        <v>1761</v>
       </c>
       <c r="G475" t="s">
-        <v>1768</v>
+        <v>1762</v>
       </c>
       <c r="H475" t="s">
-        <v>1760</v>
+        <v>1754</v>
       </c>
       <c r="I475" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="476" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="476" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A476" s="1">
         <v>474</v>
       </c>
@@ -20070,25 +20077,25 @@
         <v>9</v>
       </c>
       <c r="D476" t="s">
-        <v>1769</v>
+        <v>1763</v>
       </c>
       <c r="E476" t="s">
-        <v>1770</v>
+        <v>1764</v>
       </c>
       <c r="F476" t="s">
-        <v>1771</v>
+        <v>1765</v>
       </c>
       <c r="G476" t="s">
-        <v>1772</v>
+        <v>1766</v>
       </c>
       <c r="H476" t="s">
-        <v>1760</v>
+        <v>1754</v>
       </c>
       <c r="I476" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="477" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="477" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A477" s="1">
         <v>475</v>
       </c>
@@ -20099,25 +20106,25 @@
         <v>9</v>
       </c>
       <c r="D477" t="s">
-        <v>1773</v>
+        <v>1767</v>
       </c>
       <c r="E477" t="s">
-        <v>1774</v>
+        <v>1768</v>
       </c>
       <c r="F477" t="s">
-        <v>1775</v>
+        <v>1769</v>
       </c>
       <c r="G477" t="s">
-        <v>1776</v>
+        <v>1770</v>
       </c>
       <c r="H477" t="s">
-        <v>1760</v>
+        <v>1754</v>
       </c>
       <c r="I477" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="478" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="478" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A478" s="1">
         <v>476</v>
       </c>
@@ -20128,25 +20135,25 @@
         <v>9</v>
       </c>
       <c r="D478" t="s">
-        <v>1777</v>
+        <v>1771</v>
       </c>
       <c r="E478" t="s">
-        <v>1778</v>
+        <v>1772</v>
       </c>
       <c r="F478" t="s">
-        <v>1779</v>
+        <v>1773</v>
       </c>
       <c r="G478" t="s">
-        <v>1780</v>
+        <v>1774</v>
       </c>
       <c r="H478" t="s">
-        <v>1760</v>
+        <v>1754</v>
       </c>
       <c r="I478" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="479" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="479" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A479" s="1">
         <v>477</v>
       </c>
@@ -20157,25 +20164,25 @@
         <v>9</v>
       </c>
       <c r="D479" t="s">
-        <v>1781</v>
+        <v>1775</v>
       </c>
       <c r="E479" t="s">
-        <v>1782</v>
+        <v>1776</v>
       </c>
       <c r="F479" t="s">
-        <v>1783</v>
+        <v>1777</v>
       </c>
       <c r="G479" t="s">
-        <v>1784</v>
+        <v>1778</v>
       </c>
       <c r="H479" t="s">
-        <v>1760</v>
+        <v>1754</v>
       </c>
       <c r="I479" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="480" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="480" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A480" s="1">
         <v>478</v>
       </c>
@@ -20186,25 +20193,25 @@
         <v>9</v>
       </c>
       <c r="D480" t="s">
-        <v>1785</v>
+        <v>1779</v>
       </c>
       <c r="E480" t="s">
-        <v>1786</v>
+        <v>1780</v>
       </c>
       <c r="F480" t="s">
-        <v>1787</v>
+        <v>1781</v>
       </c>
       <c r="G480" t="s">
-        <v>1788</v>
+        <v>1782</v>
       </c>
       <c r="H480" t="s">
-        <v>1760</v>
+        <v>1754</v>
       </c>
       <c r="I480" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="481" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="481" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A481" s="1">
         <v>479</v>
       </c>
@@ -20215,25 +20222,25 @@
         <v>9</v>
       </c>
       <c r="D481" t="s">
-        <v>1789</v>
+        <v>1783</v>
       </c>
       <c r="E481" t="s">
-        <v>1790</v>
+        <v>1784</v>
       </c>
       <c r="F481" t="s">
-        <v>1791</v>
+        <v>1785</v>
       </c>
       <c r="G481" t="s">
-        <v>1792</v>
+        <v>1786</v>
       </c>
       <c r="H481" t="s">
-        <v>1760</v>
+        <v>1754</v>
       </c>
       <c r="I481" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="482" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="482" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A482" s="1">
         <v>480</v>
       </c>
@@ -20244,25 +20251,25 @@
         <v>9</v>
       </c>
       <c r="D482" t="s">
-        <v>1793</v>
+        <v>1787</v>
       </c>
       <c r="E482" t="s">
-        <v>1794</v>
+        <v>1788</v>
       </c>
       <c r="F482" t="s">
-        <v>1795</v>
+        <v>1789</v>
       </c>
       <c r="G482" t="s">
-        <v>1796</v>
+        <v>1790</v>
       </c>
       <c r="H482" t="s">
-        <v>1760</v>
+        <v>1754</v>
       </c>
       <c r="I482" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="483" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="483" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A483" s="1">
         <v>481</v>
       </c>
@@ -20273,25 +20280,25 @@
         <v>9</v>
       </c>
       <c r="D483" t="s">
-        <v>1797</v>
+        <v>1791</v>
       </c>
       <c r="E483" t="s">
-        <v>1798</v>
+        <v>1792</v>
       </c>
       <c r="F483" t="s">
-        <v>1799</v>
+        <v>1793</v>
       </c>
       <c r="G483" t="s">
-        <v>1800</v>
+        <v>1794</v>
       </c>
       <c r="H483" t="s">
-        <v>1760</v>
+        <v>1754</v>
       </c>
       <c r="I483" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="484" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="484" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A484" s="1">
         <v>482</v>
       </c>
@@ -20302,25 +20309,25 @@
         <v>9</v>
       </c>
       <c r="D484" t="s">
-        <v>1801</v>
+        <v>1795</v>
       </c>
       <c r="E484" t="s">
-        <v>1802</v>
+        <v>1796</v>
       </c>
       <c r="F484" t="s">
-        <v>1803</v>
+        <v>1797</v>
       </c>
       <c r="G484" t="s">
-        <v>1804</v>
+        <v>1798</v>
       </c>
       <c r="H484" t="s">
-        <v>1760</v>
+        <v>1754</v>
       </c>
       <c r="I484" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="485" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="485" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A485" s="1">
         <v>483</v>
       </c>
@@ -20331,25 +20338,25 @@
         <v>9</v>
       </c>
       <c r="D485" t="s">
-        <v>1805</v>
+        <v>1799</v>
       </c>
       <c r="E485" t="s">
-        <v>1806</v>
+        <v>1800</v>
       </c>
       <c r="F485" t="s">
-        <v>1807</v>
+        <v>1801</v>
       </c>
       <c r="G485" t="s">
-        <v>1808</v>
+        <v>1802</v>
       </c>
       <c r="H485" t="s">
-        <v>1760</v>
+        <v>1754</v>
       </c>
       <c r="I485" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="486" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="486" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A486" s="1">
         <v>484</v>
       </c>
@@ -20360,25 +20367,25 @@
         <v>9</v>
       </c>
       <c r="D486" t="s">
-        <v>1809</v>
+        <v>1803</v>
       </c>
       <c r="E486" t="s">
-        <v>1810</v>
+        <v>1804</v>
       </c>
       <c r="F486" t="s">
-        <v>1811</v>
+        <v>1805</v>
       </c>
       <c r="G486" t="s">
-        <v>1812</v>
+        <v>1806</v>
       </c>
       <c r="H486" t="s">
-        <v>1760</v>
+        <v>1754</v>
       </c>
       <c r="I486" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="487" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="487" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A487" s="1">
         <v>485</v>
       </c>
@@ -20389,25 +20396,25 @@
         <v>9</v>
       </c>
       <c r="D487" t="s">
-        <v>1813</v>
+        <v>1807</v>
       </c>
       <c r="E487" t="s">
-        <v>1814</v>
+        <v>1808</v>
       </c>
       <c r="F487" t="s">
-        <v>1815</v>
+        <v>1809</v>
       </c>
       <c r="G487" t="s">
-        <v>1816</v>
+        <v>1810</v>
       </c>
       <c r="H487" t="s">
-        <v>1760</v>
+        <v>1754</v>
       </c>
       <c r="I487" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="488" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="488" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A488" s="1">
         <v>486</v>
       </c>
@@ -20418,25 +20425,25 @@
         <v>9</v>
       </c>
       <c r="D488" t="s">
-        <v>1817</v>
+        <v>1811</v>
       </c>
       <c r="E488" t="s">
-        <v>1818</v>
+        <v>1812</v>
       </c>
       <c r="F488" t="s">
-        <v>1819</v>
+        <v>1813</v>
       </c>
       <c r="G488" t="s">
-        <v>1820</v>
+        <v>1814</v>
       </c>
       <c r="H488" t="s">
-        <v>1760</v>
+        <v>1754</v>
       </c>
       <c r="I488" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="489" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="489" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A489" s="1">
         <v>487</v>
       </c>
@@ -20447,25 +20454,25 @@
         <v>9</v>
       </c>
       <c r="D489" t="s">
-        <v>1821</v>
+        <v>1815</v>
       </c>
       <c r="E489" t="s">
-        <v>1822</v>
+        <v>1816</v>
       </c>
       <c r="F489" t="s">
-        <v>1823</v>
+        <v>1817</v>
       </c>
       <c r="G489" t="s">
-        <v>1824</v>
+        <v>1818</v>
       </c>
       <c r="H489" t="s">
-        <v>1760</v>
+        <v>1754</v>
       </c>
       <c r="I489" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="490" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="490" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A490" s="1">
         <v>488</v>
       </c>
@@ -20476,25 +20483,25 @@
         <v>9</v>
       </c>
       <c r="D490" t="s">
-        <v>1825</v>
+        <v>1819</v>
       </c>
       <c r="E490" t="s">
-        <v>1826</v>
+        <v>1820</v>
       </c>
       <c r="F490" t="s">
-        <v>1827</v>
+        <v>1821</v>
       </c>
       <c r="G490" t="s">
-        <v>1828</v>
+        <v>1822</v>
       </c>
       <c r="H490" t="s">
-        <v>1760</v>
+        <v>1754</v>
       </c>
       <c r="I490" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="491" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="491" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A491" s="1">
         <v>489</v>
       </c>
@@ -20505,25 +20512,25 @@
         <v>9</v>
       </c>
       <c r="D491" t="s">
-        <v>1829</v>
+        <v>1823</v>
       </c>
       <c r="E491" t="s">
-        <v>1830</v>
+        <v>1824</v>
       </c>
       <c r="F491" t="s">
-        <v>1831</v>
+        <v>1825</v>
       </c>
       <c r="G491" t="s">
-        <v>1832</v>
+        <v>1826</v>
       </c>
       <c r="H491" t="s">
-        <v>1760</v>
+        <v>1754</v>
       </c>
       <c r="I491" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="492" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="492" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A492" s="1">
         <v>490</v>
       </c>
@@ -20534,25 +20541,25 @@
         <v>9</v>
       </c>
       <c r="D492" t="s">
-        <v>1833</v>
+        <v>1827</v>
       </c>
       <c r="E492" t="s">
-        <v>1834</v>
+        <v>1828</v>
       </c>
       <c r="F492" t="s">
-        <v>1835</v>
+        <v>1829</v>
       </c>
       <c r="G492" t="s">
-        <v>1836</v>
+        <v>1830</v>
       </c>
       <c r="H492" t="s">
-        <v>1760</v>
+        <v>1754</v>
       </c>
       <c r="I492" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="493" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="493" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A493" s="1">
         <v>491</v>
       </c>
@@ -20563,25 +20570,25 @@
         <v>9</v>
       </c>
       <c r="D493" t="s">
-        <v>1837</v>
+        <v>1831</v>
       </c>
       <c r="E493" t="s">
-        <v>1838</v>
+        <v>1832</v>
       </c>
       <c r="F493" t="s">
-        <v>1839</v>
+        <v>1833</v>
       </c>
       <c r="G493" t="s">
-        <v>1840</v>
+        <v>1834</v>
       </c>
       <c r="H493" t="s">
-        <v>1760</v>
+        <v>1754</v>
       </c>
       <c r="I493" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="494" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="494" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A494" s="1">
         <v>492</v>
       </c>
@@ -20592,25 +20599,25 @@
         <v>9</v>
       </c>
       <c r="D494" t="s">
-        <v>1841</v>
+        <v>1835</v>
       </c>
       <c r="E494" t="s">
-        <v>1842</v>
+        <v>1836</v>
       </c>
       <c r="F494" t="s">
-        <v>1843</v>
+        <v>1837</v>
       </c>
       <c r="G494" t="s">
-        <v>1844</v>
+        <v>1838</v>
       </c>
       <c r="H494" t="s">
-        <v>1760</v>
+        <v>1754</v>
       </c>
       <c r="I494" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="495" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="495" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A495" s="1">
         <v>493</v>
       </c>
@@ -20621,25 +20628,25 @@
         <v>9</v>
       </c>
       <c r="D495" t="s">
-        <v>1845</v>
+        <v>1839</v>
       </c>
       <c r="E495" t="s">
-        <v>1846</v>
+        <v>1840</v>
       </c>
       <c r="F495" t="s">
-        <v>1847</v>
+        <v>1841</v>
       </c>
       <c r="G495" t="s">
-        <v>1848</v>
+        <v>1842</v>
       </c>
       <c r="H495" t="s">
-        <v>1760</v>
+        <v>1754</v>
       </c>
       <c r="I495" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="496" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="496" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A496" s="1">
         <v>494</v>
       </c>
@@ -20650,25 +20657,25 @@
         <v>9</v>
       </c>
       <c r="D496" t="s">
-        <v>1849</v>
+        <v>1843</v>
       </c>
       <c r="E496" t="s">
-        <v>1850</v>
+        <v>1844</v>
       </c>
       <c r="F496" t="s">
-        <v>1851</v>
+        <v>1845</v>
       </c>
       <c r="G496" t="s">
-        <v>1852</v>
+        <v>1846</v>
       </c>
       <c r="H496" t="s">
-        <v>1760</v>
+        <v>1754</v>
       </c>
       <c r="I496" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="497" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="497" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A497" s="1">
         <v>495</v>
       </c>
@@ -20679,25 +20686,25 @@
         <v>9</v>
       </c>
       <c r="D497" t="s">
-        <v>1853</v>
+        <v>1847</v>
       </c>
       <c r="E497" t="s">
-        <v>1854</v>
+        <v>1848</v>
       </c>
       <c r="F497" t="s">
-        <v>1855</v>
+        <v>1849</v>
       </c>
       <c r="G497" t="s">
-        <v>1856</v>
+        <v>1850</v>
       </c>
       <c r="H497" t="s">
-        <v>1760</v>
+        <v>1754</v>
       </c>
       <c r="I497" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="498" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="498" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A498" s="1">
         <v>496</v>
       </c>
@@ -20708,25 +20715,25 @@
         <v>9</v>
       </c>
       <c r="D498" t="s">
-        <v>1857</v>
+        <v>1851</v>
       </c>
       <c r="E498" t="s">
-        <v>1858</v>
+        <v>1852</v>
       </c>
       <c r="F498" t="s">
-        <v>1859</v>
+        <v>1853</v>
       </c>
       <c r="G498" t="s">
-        <v>1860</v>
+        <v>1854</v>
       </c>
       <c r="H498" t="s">
-        <v>1861</v>
+        <v>1855</v>
       </c>
       <c r="I498" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="499" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="499" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A499" s="1">
         <v>497</v>
       </c>
@@ -20737,25 +20744,25 @@
         <v>9</v>
       </c>
       <c r="D499" t="s">
-        <v>1862</v>
+        <v>1856</v>
       </c>
       <c r="E499" t="s">
-        <v>1863</v>
+        <v>1857</v>
       </c>
       <c r="F499" t="s">
-        <v>1864</v>
+        <v>1858</v>
       </c>
       <c r="G499" t="s">
-        <v>1865</v>
+        <v>1859</v>
       </c>
       <c r="H499" t="s">
-        <v>1861</v>
+        <v>1855</v>
       </c>
       <c r="I499" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="500" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="500" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A500" s="1">
         <v>498</v>
       </c>
@@ -20766,25 +20773,25 @@
         <v>9</v>
       </c>
       <c r="D500" t="s">
-        <v>1866</v>
+        <v>1860</v>
       </c>
       <c r="E500" t="s">
-        <v>1867</v>
+        <v>1861</v>
       </c>
       <c r="F500" t="s">
-        <v>1868</v>
+        <v>1862</v>
       </c>
       <c r="G500" t="s">
-        <v>1869</v>
+        <v>1863</v>
       </c>
       <c r="H500" t="s">
-        <v>1861</v>
+        <v>1855</v>
       </c>
       <c r="I500" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="501" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="501" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A501" s="1">
         <v>499</v>
       </c>
@@ -20795,25 +20802,25 @@
         <v>9</v>
       </c>
       <c r="D501" t="s">
-        <v>1870</v>
+        <v>1864</v>
       </c>
       <c r="E501" t="s">
-        <v>1871</v>
+        <v>1865</v>
       </c>
       <c r="F501" t="s">
-        <v>1872</v>
+        <v>1866</v>
       </c>
       <c r="G501" t="s">
-        <v>1873</v>
+        <v>1867</v>
       </c>
       <c r="H501" t="s">
-        <v>1861</v>
+        <v>1855</v>
       </c>
       <c r="I501" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="502" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="502" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A502" s="1">
         <v>500</v>
       </c>
@@ -20824,25 +20831,25 @@
         <v>9</v>
       </c>
       <c r="D502" t="s">
-        <v>1874</v>
+        <v>1868</v>
       </c>
       <c r="E502" t="s">
-        <v>1875</v>
+        <v>1869</v>
       </c>
       <c r="F502" t="s">
-        <v>1876</v>
+        <v>1870</v>
       </c>
       <c r="G502" t="s">
-        <v>1877</v>
+        <v>1871</v>
       </c>
       <c r="H502" t="s">
-        <v>1878</v>
+        <v>1872</v>
       </c>
       <c r="I502" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="503" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="503" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A503" s="1">
         <v>501</v>
       </c>
@@ -20853,25 +20860,25 @@
         <v>9</v>
       </c>
       <c r="D503" t="s">
-        <v>1879</v>
+        <v>1873</v>
       </c>
       <c r="E503" t="s">
-        <v>1880</v>
+        <v>1874</v>
       </c>
       <c r="F503" t="s">
-        <v>1881</v>
+        <v>1875</v>
       </c>
       <c r="G503" t="s">
-        <v>1882</v>
+        <v>1876</v>
       </c>
       <c r="H503" t="s">
-        <v>1883</v>
+        <v>1877</v>
       </c>
       <c r="I503" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="504" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="504" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A504" s="1">
         <v>502</v>
       </c>
@@ -20882,25 +20889,25 @@
         <v>9</v>
       </c>
       <c r="D504" t="s">
-        <v>1884</v>
+        <v>1878</v>
       </c>
       <c r="E504" t="s">
-        <v>1885</v>
+        <v>1879</v>
       </c>
       <c r="F504" t="s">
-        <v>1886</v>
+        <v>1880</v>
       </c>
       <c r="G504" t="s">
-        <v>1887</v>
+        <v>1881</v>
       </c>
       <c r="H504" t="s">
-        <v>1883</v>
+        <v>1877</v>
       </c>
       <c r="I504" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="505" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="505" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A505" s="1">
         <v>503</v>
       </c>
@@ -20911,25 +20918,25 @@
         <v>9</v>
       </c>
       <c r="D505" t="s">
-        <v>1888</v>
+        <v>1882</v>
       </c>
       <c r="E505" t="s">
-        <v>1889</v>
+        <v>1883</v>
       </c>
       <c r="F505" t="s">
-        <v>1890</v>
+        <v>1884</v>
       </c>
       <c r="G505" t="s">
-        <v>1891</v>
+        <v>1885</v>
       </c>
       <c r="H505" t="s">
-        <v>1892</v>
+        <v>1886</v>
       </c>
       <c r="I505" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="506" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="506" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A506" s="1">
         <v>504</v>
       </c>
@@ -20940,25 +20947,25 @@
         <v>9</v>
       </c>
       <c r="D506" t="s">
-        <v>1893</v>
+        <v>1887</v>
       </c>
       <c r="E506" t="s">
-        <v>1894</v>
+        <v>1888</v>
       </c>
       <c r="F506" t="s">
-        <v>1895</v>
+        <v>1889</v>
       </c>
       <c r="G506" t="s">
-        <v>1896</v>
+        <v>1890</v>
       </c>
       <c r="H506" t="s">
-        <v>1892</v>
+        <v>1886</v>
       </c>
       <c r="I506" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="507" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="507" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A507" s="1">
         <v>505</v>
       </c>
@@ -20969,25 +20976,25 @@
         <v>9</v>
       </c>
       <c r="D507" t="s">
-        <v>1897</v>
+        <v>1891</v>
       </c>
       <c r="E507" t="s">
-        <v>1898</v>
+        <v>1892</v>
       </c>
       <c r="F507" t="s">
-        <v>1899</v>
+        <v>1893</v>
       </c>
       <c r="G507" t="s">
-        <v>1900</v>
+        <v>1894</v>
       </c>
       <c r="H507" t="s">
-        <v>1892</v>
+        <v>1886</v>
       </c>
       <c r="I507" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="508" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="508" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A508" s="1">
         <v>506</v>
       </c>
@@ -20998,25 +21005,25 @@
         <v>9</v>
       </c>
       <c r="D508" t="s">
-        <v>1901</v>
+        <v>1895</v>
       </c>
       <c r="E508" t="s">
-        <v>1902</v>
+        <v>1896</v>
       </c>
       <c r="F508" t="s">
-        <v>1903</v>
+        <v>1897</v>
       </c>
       <c r="G508" t="s">
-        <v>1904</v>
+        <v>1898</v>
       </c>
       <c r="H508" t="s">
-        <v>1760</v>
+        <v>1754</v>
       </c>
       <c r="I508" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="509" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="509" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A509" s="1">
         <v>507</v>
       </c>
@@ -21027,25 +21034,25 @@
         <v>9</v>
       </c>
       <c r="D509" t="s">
-        <v>1905</v>
+        <v>1899</v>
       </c>
       <c r="E509" t="s">
-        <v>1906</v>
+        <v>1900</v>
       </c>
       <c r="F509" t="s">
-        <v>1907</v>
+        <v>1901</v>
       </c>
       <c r="G509" t="s">
-        <v>1908</v>
+        <v>1902</v>
       </c>
       <c r="H509" t="s">
-        <v>1760</v>
+        <v>1754</v>
       </c>
       <c r="I509" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="510" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="510" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A510" s="1">
         <v>508</v>
       </c>
@@ -21056,25 +21063,25 @@
         <v>9</v>
       </c>
       <c r="D510" t="s">
-        <v>1909</v>
+        <v>1903</v>
       </c>
       <c r="E510" t="s">
-        <v>1910</v>
+        <v>1904</v>
       </c>
       <c r="F510" t="s">
-        <v>1911</v>
+        <v>1905</v>
       </c>
       <c r="G510" t="s">
-        <v>1912</v>
+        <v>1906</v>
       </c>
       <c r="H510" t="s">
-        <v>1760</v>
+        <v>1754</v>
       </c>
       <c r="I510" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="511" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="511" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A511" s="1">
         <v>509</v>
       </c>
@@ -21085,25 +21092,25 @@
         <v>9</v>
       </c>
       <c r="D511" t="s">
-        <v>1913</v>
+        <v>1907</v>
       </c>
       <c r="E511" t="s">
-        <v>1914</v>
+        <v>1908</v>
       </c>
       <c r="F511" t="s">
-        <v>1915</v>
+        <v>1909</v>
       </c>
       <c r="G511" t="s">
-        <v>1916</v>
+        <v>1910</v>
       </c>
       <c r="H511" t="s">
-        <v>1760</v>
+        <v>1754</v>
       </c>
       <c r="I511" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="512" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="512" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A512" s="1">
         <v>510</v>
       </c>
@@ -21114,25 +21121,25 @@
         <v>9</v>
       </c>
       <c r="D512" t="s">
-        <v>1917</v>
+        <v>1911</v>
       </c>
       <c r="E512" t="s">
-        <v>1918</v>
+        <v>1912</v>
       </c>
       <c r="F512" t="s">
-        <v>1919</v>
+        <v>1913</v>
       </c>
       <c r="G512" t="s">
-        <v>1920</v>
+        <v>1914</v>
       </c>
       <c r="H512" t="s">
-        <v>1760</v>
+        <v>1754</v>
       </c>
       <c r="I512" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="513" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="513" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A513" s="1">
         <v>511</v>
       </c>
@@ -21143,25 +21150,25 @@
         <v>9</v>
       </c>
       <c r="D513" t="s">
-        <v>1921</v>
+        <v>1915</v>
       </c>
       <c r="E513" t="s">
-        <v>1922</v>
+        <v>1916</v>
       </c>
       <c r="F513" t="s">
-        <v>1923</v>
+        <v>1917</v>
       </c>
       <c r="G513" t="s">
-        <v>1924</v>
+        <v>1918</v>
       </c>
       <c r="H513" t="s">
-        <v>1760</v>
+        <v>1754</v>
       </c>
       <c r="I513" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="514" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="514" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A514" s="1">
         <v>512</v>
       </c>
@@ -21172,25 +21179,25 @@
         <v>9</v>
       </c>
       <c r="D514" t="s">
-        <v>1925</v>
+        <v>1919</v>
       </c>
       <c r="E514" t="s">
-        <v>1926</v>
+        <v>1920</v>
       </c>
       <c r="F514" t="s">
-        <v>1927</v>
+        <v>1921</v>
       </c>
       <c r="G514" t="s">
-        <v>1928</v>
+        <v>1922</v>
       </c>
       <c r="H514" t="s">
-        <v>1760</v>
+        <v>1754</v>
       </c>
       <c r="I514" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="515" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="515" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A515" s="1">
         <v>513</v>
       </c>
@@ -21201,25 +21208,25 @@
         <v>9</v>
       </c>
       <c r="D515" t="s">
-        <v>1929</v>
+        <v>1923</v>
       </c>
       <c r="E515" t="s">
-        <v>1930</v>
+        <v>1924</v>
       </c>
       <c r="F515" t="s">
-        <v>1931</v>
+        <v>1925</v>
       </c>
       <c r="G515" t="s">
-        <v>1932</v>
+        <v>1926</v>
       </c>
       <c r="H515" t="s">
-        <v>1760</v>
+        <v>1754</v>
       </c>
       <c r="I515" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="516" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="516" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A516" s="1">
         <v>514</v>
       </c>
@@ -21230,25 +21237,25 @@
         <v>9</v>
       </c>
       <c r="D516" t="s">
-        <v>1933</v>
+        <v>1927</v>
       </c>
       <c r="E516" t="s">
-        <v>1934</v>
+        <v>1928</v>
       </c>
       <c r="F516" t="s">
-        <v>1935</v>
+        <v>1929</v>
       </c>
       <c r="G516" t="s">
-        <v>1936</v>
+        <v>1930</v>
       </c>
       <c r="H516" t="s">
-        <v>1760</v>
+        <v>1754</v>
       </c>
       <c r="I516" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="517" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="517" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A517" s="1">
         <v>515</v>
       </c>
@@ -21259,25 +21266,25 @@
         <v>9</v>
       </c>
       <c r="D517" t="s">
-        <v>1937</v>
+        <v>1931</v>
       </c>
       <c r="E517" t="s">
-        <v>1938</v>
+        <v>1932</v>
       </c>
       <c r="F517" t="s">
-        <v>1939</v>
+        <v>1933</v>
       </c>
       <c r="G517" t="s">
-        <v>1940</v>
+        <v>1934</v>
       </c>
       <c r="H517" t="s">
-        <v>1760</v>
+        <v>1754</v>
       </c>
       <c r="I517" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="518" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="518" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A518" s="1">
         <v>516</v>
       </c>
@@ -21288,25 +21295,25 @@
         <v>9</v>
       </c>
       <c r="D518" t="s">
-        <v>1941</v>
+        <v>1935</v>
       </c>
       <c r="E518" t="s">
-        <v>1942</v>
+        <v>1936</v>
       </c>
       <c r="F518" t="s">
-        <v>1943</v>
+        <v>1937</v>
       </c>
       <c r="G518" t="s">
-        <v>1944</v>
+        <v>1938</v>
       </c>
       <c r="H518" t="s">
-        <v>1945</v>
+        <v>1939</v>
       </c>
       <c r="I518" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="519" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="519" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A519" s="1">
         <v>517</v>
       </c>
@@ -21317,22 +21324,22 @@
         <v>9</v>
       </c>
       <c r="D519" t="s">
-        <v>1946</v>
+        <v>1963</v>
       </c>
       <c r="E519" t="s">
-        <v>1947</v>
+        <v>1940</v>
       </c>
       <c r="F519" t="s">
-        <v>1948</v>
+        <v>1941</v>
       </c>
       <c r="G519" t="s">
-        <v>1949</v>
+        <v>1942</v>
       </c>
       <c r="H519" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="520" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="520" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A520" s="1">
         <v>518</v>
       </c>
@@ -21343,16 +21350,16 @@
         <v>9</v>
       </c>
       <c r="D520" t="s">
-        <v>1950</v>
+        <v>1943</v>
       </c>
       <c r="E520" t="s">
-        <v>1951</v>
+        <v>1944</v>
       </c>
       <c r="F520" t="s">
-        <v>1952</v>
+        <v>1945</v>
       </c>
       <c r="G520" t="s">
-        <v>1953</v>
+        <v>1946</v>
       </c>
       <c r="H520" t="s">
         <v>14</v>
